--- a/28car_潛客_100條.xlsx
+++ b/28car_潛客_100條.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G101"/>
+  <dimension ref="A1:F158"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -456,11 +456,6 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>頁碼</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
           <t>創建時間</t>
         </is>
       </c>
@@ -468,2463 +463,2072 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>59766617</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>car88@myyahoo.com</t>
-        </is>
-      </c>
+          <t>93343280</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr">
         <is>
-          <t>平治 190 E2.5 16V 汽油 4座 2498cc 自動波 1989 $268,000 1 97</t>
+          <t>豐田</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>大發 WAKE G NBOX	汽油	4座	660cc	自動波	2018	$68,888	1	91 | 彩籃色 雙電門 3缸Turbo 恆溫冷氣 Android音響...，Vins 電郵:car88@myyahoo.com | 豐田 PRIUS 1.8 HYBRID S	混能	5座	1800cc	自動波	2018	$128,000	0	888</t>
+          <t>燃炓	座位	動力	傳動	年份	售價	留言	瀏覽	已售 | 寶馬 218i ACTIVE TOURER	汽油	5座	1500cc	自動波	2015	$45,000	1	1829 | 越野路華 VELAR P250	汽油	5座	1997cc	自動波	2017	$188,000	0	198</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>page_1_line_4837</t>
-        </is>
-      </c>
-      <c r="F2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>2026-03-20 13:58:38</t>
+          <t>page_1_line_4595</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>2026-04-03 07:02:35</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>60878617</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>car88@myyahoo.com</t>
-        </is>
-      </c>
+          <t>92580664</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr"/>
       <c r="C3" t="inlineStr">
         <is>
-          <t>凌志 GS200T 2.0 Turbo 汽油 5座 2000cc 自動波 2017 $105,800 0 42</t>
+          <t>豐田</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>五十鈴 5.5TONNES	柴油	3座	5193cc	棍波	2015	$148,000	0	1045 | 鈴木 Jimny JB74W	汽油	4座	1500cc	自動波	2024	$178,888	1	123 | 行貨 自動波 恆溫冷氣 Alpine音響 360鏡頭 mor...，Vins 電郵:car88@myyahoo.com</t>
+          <t>寶馬 118i M SPORT 116I	汽油	5座	1600cc	自動波	2013	$33,800	0	679 | 本田 FREED G	汽油	6座	1500cc	自動波	2008	$29,300	0	3635 | 奧迪 Q5 2.0 QUATTRO	汽油	5座	2000cc	自動波	2012	$33,020	1	2939</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>page_1_line_4821</t>
-        </is>
-      </c>
-      <c r="F3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>2026-03-20 13:58:38</t>
+          <t>page_1_line_4623</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>2026-04-03 07:02:35</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>61822201</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>car88@myyahoo.com</t>
-        </is>
-      </c>
+          <t>93180295</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr">
         <is>
-          <t>豐田 ALPHARD ZA 汽油 7座 2500cc 自動波 2020 $248,000 1 3902</t>
+          <t>豐田</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>本田 ODYSSEY HYBRID ABSOLUTE EX	混能	7座	2000cc	自動波	2018	$138,000	1	3187 | 豐田 ALPHARD 2.5 SC VELLFIRE	汽油	7座	2500cc	自動波	2023	$388,008	1	1108 | 黑色 雙天窗 3電門 4電坐 冷暖坐 空氣淨化 DVD BT...，Vins 電郵:car88@myyahoo.com</t>
+          <t>本田 FREED G	汽油	6座	1500cc	自動波	2008	$29,300	0	3635 | 奧迪 Q5 2.0 QUATTRO	汽油	5座	2000cc	自動波	2012	$33,020	1	2939 | 豐田 ALPHARD 3.5	汽油	7座	3456cc	自動波	2018	$296,000	1	700</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>page_1_line_4861</t>
-        </is>
-      </c>
-      <c r="F4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>2026-03-20 13:58:38</t>
+          <t>page_1_line_4627</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>2026-04-03 07:02:35</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>62633422</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>car88@myyahoo.com</t>
-        </is>
-      </c>
+          <t>53270102</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr">
         <is>
-          <t>保時捷 BOXSTER S 汽油 2座 3400cc 自動波 2006 $75,000 0 3741</t>
+          <t>寶馬</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>豐田 GR86 RZ EYESIGHT	汽油	4座	2400cc	棍波	2024	$398,000	0	401 | 豐田 VELLFIRE ZG	汽油	7座	2500cc	自動波	2016	$178,000	1	2124 | 保時捷 BOXSTER S	汽油	2座	3400cc	自動波	2006	$75,000	0	3741</t>
+          <t>豐田 ALPHARD 3.5 SC FACELIFT	汽油	7座	3456cc	自動波	2018	$315,001	1	7006 | 豐田 ALPHARD 3.5 SC FACELIFT	汽油	7座	3456cc	自動波	2018	$315,001	1	9224 | 奧迪 S5 CAB 3.0 TFSI QUATTRO	汽油	4座	2995cc	自動波	2013	$85,001	0	3877</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>page_1_line_4885</t>
-        </is>
-      </c>
-      <c r="F5" t="n">
-        <v>1</v>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>2026-03-20 13:58:38</t>
+          <t>page_1_line_4663</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>2026-04-03 07:02:35</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>90703526</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>car88@myyahoo.com</t>
-        </is>
-      </c>
+          <t>64388789</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr">
         <is>
-          <t>五十鈴 5.5TONNES 柴油 3座 5193cc 棍波 2022 $326,800 1 280</t>
+          <t>平治</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>豐田 VOXY HYBRID ZS NOAH	混能	7座	1800cc	自動波	2019	$188,008	2	964 | 白色 黑皮 雙電門 電尾冚 Alpine音響 ...，Vins 電郵:car88@myyahoo.com | 平治 E250 CAB E200	汽油	4座	2000cc	自動波	2015	$78,800	1	2609</t>
+          <t>燃炓	座位	動力	傳動	年份	售價	留言	瀏覽	已售 | 平治 GLC300 AMG EQBOOST	汽油	5座	2000cc	自動波	2020	$268,000	0	462 | 豐田 SIENTA	汽油	7座	1500cc	自動波	2023	$188,800	0	531</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>page_1_line_4849</t>
-        </is>
-      </c>
-      <c r="F6" t="n">
-        <v>1</v>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>2026-03-20 13:58:38</t>
+          <t>page_1_line_4969</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>2026-04-02 07:00:19</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>90787669</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>car88@myyahoo.com</t>
-        </is>
-      </c>
+          <t>96008558</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr">
         <is>
-          <t>五十鈴 5.5TONNES 柴油 3座 5193cc 棍波 2017 $188,000 0 1156</t>
+          <t>現代</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>燃炓	座位	動力	傳動	年份	售價	留言	瀏覽	已售 | 五十鈴 5.5TONNES	柴油	3座	5193cc	棍波	2017	$188,000	0	1156 | 五十鈴 5.5TONNES	柴油	3座	5193cc	棍波	2015	$148,000	0	1045</t>
+          <t>寶馬 630GT SPORT	汽油	5座	2000cc	自動波	2018	$158,800	0	805 | 寶馬 M4 COMPETITION	汽油	4座	3000cc	自動波	2021	$848,000	0	1363 | 法拉利 F458 SPIDER	汽油	2座	4500cc	自動波	2014	$1,388,800	0	5249</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>page_1_line_4809</t>
-        </is>
-      </c>
-      <c r="F7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>2026-03-20 13:58:38</t>
+          <t>page_1_line_4989</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>2026-04-02 07:00:19</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>91232229</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>car88@myyahoo.com</t>
-        </is>
-      </c>
+          <t>94448758</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr"/>
       <c r="C8" t="inlineStr">
         <is>
-          <t>迷你 MINI Cooper S ROADSTER 汽油 2座 1598cc 自動波 2014 $148,000 0 169</t>
+          <t>奧迪</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>燃炓	座位	動力	傳動	年份	售價	留言	瀏覽	已售 | 五十鈴 MVD	柴油	3座	5200cc	棍波	2016	$180,000	0	0 | 五十鈴 24TONNES	柴油	3座	15681cc	棍波	2019	$427,800	0	346</t>
+          <t>法拉利 F458 SPIDER	汽油	2座	4500cc	自動波	2014	$1,388,800	0	5249 | 現代 H1	柴油	5座	2497cc	自動波	2013	$90,000	0	502 | 平治 VITO 116 CDI	柴油	5座	2143cc	自動波	2013	$79,000	0	3211</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>page_1_line_4821</t>
-        </is>
-      </c>
-      <c r="F8" t="n">
-        <v>1</v>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>2026-03-20 14:00:35</t>
+          <t>page_1_line_4997</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>2026-04-02 07:00:19</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>91750024</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>car88@myyahoo.com</t>
-        </is>
-      </c>
+          <t>91517374</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr"/>
       <c r="C9" t="inlineStr">
         <is>
-          <t>豐田 NOAH 90 汽油 7座 1987cc 自動波 2023 $269,000 0 4562</t>
+          <t>豐田</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>豐田 ALPHARD 2.5 SC VELLFIRE	汽油	7座	2500cc	自動波	2023	$388,008	1	1108 | 黑色 雙天窗 3電門 4電坐 冷暖坐 空氣淨化 DVD BT...，Vins 電郵:car88@myyahoo.com | 豐田 ALPHARD ZA	汽油	7座	2500cc	自動波	2020	$248,000	1	3902</t>
+          <t>寶馬 316I	汽油	5座	1600cc	自動波	2013	$32,800	0	72 | 平治 E350	汽油	5座	3500cc	自動波	2013	$68,200	0	50 | 本田 FREED G	汽油	6座	1500cc	自動波	2008	$29,200	0	3599</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>page_1_line_4865</t>
-        </is>
-      </c>
-      <c r="F9" t="n">
-        <v>1</v>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>2026-03-20 13:58:38</t>
+          <t>page_1_line_5029</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>2026-04-02 07:00:19</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>95006400</t>
+          <t>95184435</t>
         </is>
       </c>
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="inlineStr">
         <is>
-          <t>五十鈴 MVD 柴油 3座 5200cc 棍波 2016 $180,000 0 0</t>
+          <t>豐田</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>燃炓	座位	動力	傳動	年份	售價	留言	瀏覽	已售 | 五十鈴 MVD	柴油	3座	5200cc	棍波	2016	$180,000	0	0 | 五十鈴 24TONNES	柴油	3座	15681cc	棍波	2019	$427,800	0	346</t>
+          <t>平治 E350	汽油	5座	3500cc	自動波	2013	$68,200	0	50 | 本田 FREED G	汽油	6座	1500cc	自動波	2008	$29,200	0	3599 | 豐田 Corolla CROSS	混能	5座	1987cc	自動波	2024	$186,000	0	132</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>page_1_line_4809</t>
-        </is>
-      </c>
-      <c r="F10" t="n">
-        <v>1</v>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>2026-03-20 14:00:35</t>
+          <t>page_1_line_5033</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>2026-04-02 07:00:19</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>98088522</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>car88@myyahoo.com</t>
-        </is>
-      </c>
+          <t>67751011</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr"/>
       <c r="C11" t="inlineStr">
         <is>
-          <t>平治 E250 CAB E200 汽油 4座 2000cc 自動波 2015 $78,800 1 2609</t>
+          <t>現代</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>平治 190 E2.5 16V	汽油	4座	2498cc	自動波	1989	$268,000	1	97 | 豐田 VOXY HYBRID ZS NOAH	混能	7座	1800cc	自動波	2019	$188,008	2	964 | 白色 黑皮 雙電門 電尾冚 Alpine音響 ...，Vins 電郵:car88@myyahoo.com</t>
+          <t>本田 FREED G	汽油	6座	1500cc	自動波	2008	$29,200	0	3599 | 豐田 Corolla CROSS	混能	5座	1987cc	自動波	2024	$186,000	0	132 | 豐田 SPADE	汽油	5座	1496cc	自動波	2013	$37,499	1	9</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>page_1_line_4845</t>
-        </is>
-      </c>
-      <c r="F11" t="n">
-        <v>1</v>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>2026-03-20 13:58:38</t>
+          <t>page_1_line_5037</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>2026-04-02 07:00:19</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>98835057</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>car88@myyahoo.com</t>
-        </is>
-      </c>
+          <t>68991904</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr"/>
       <c r="C12" t="inlineStr">
         <is>
-          <t>豐田 PRIUS 1.8 HYBRID S 混能 5座 1800cc 自動波 2018 $128,000 0 888</t>
+          <t>平治</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>任何 R3	汽油	2座	300cc	棍波	2016	$15,000	1	1244 | 有意WhatsApp、牌費到7月、要換消耗品 (由於已售，聯絡人資料亦被保護中。) | 大發 WAKE G NBOX	汽油	4座	660cc	自動波	2018	$68,888	1	91</t>
+          <t>豐田 Corolla CROSS	混能	5座	1987cc	自動波	2024	$186,000	0	132 | 豐田 SPADE	汽油	5座	1496cc	自動波	2013	$37,499	1	9 | 現代 H1 EURO 5	柴油	5座	2497cc	自動波	2015	$42,000	0	2</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>page_1_line_4833</t>
-        </is>
-      </c>
-      <c r="F12" t="n">
-        <v>1</v>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>2026-03-20 13:58:38</t>
+          <t>page_1_line_5041</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2026-04-02 07:00:19</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>62559898</t>
+          <t>51004509</t>
         </is>
       </c>
       <c r="B13" t="inlineStr"/>
       <c r="C13" t="inlineStr">
         <is>
-          <t>本田 FREED HYBRID 混能 6座 1500cc 自動波 2012 $45,000 0 1395</t>
+          <t>豐田</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>保時捷 GT3 RS	汽油	2座	3600cc	棍波	2007	$1,475,000	1	4966 | 豐田 ALPHARD 3.5 SC FACELIFT	汽油	7座	3500cc	自動波	2022	$389,000	1	1707 | 本田 FREED HYBRID	混能	6座	1500cc	自動波	2012	$45,000	0	1395</t>
+          <t>豐田 SPADE	汽油	5座	1496cc	自動波	2013	$37,499	1	9 | 現代 H1 EURO 5	柴油	5座	2497cc	自動波	2015	$42,000	0	2 | 平治 C200 AMG FL	汽油	5座	1497cc	自動波	2021	$178,000	0	2197</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>page_2_line_4881</t>
-        </is>
-      </c>
-      <c r="F13" t="n">
-        <v>2</v>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>2026-03-20 14:00:45</t>
+          <t>page_1_line_5045</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2026-04-02 07:00:19</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>54346258</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>js321@myyahoo.com</t>
-        </is>
-      </c>
+          <t>92070184</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr"/>
       <c r="C14" t="inlineStr">
         <is>
-          <t>平治 S580L AMG 汽油 5座 4000cc 自動波 2023 $1,680,000 0 1236</t>
+          <t>寶馬</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>豐田 VOXY HYBRID FACELIFT NOAH	混能	7座	1800cc	自動波	2021	$208,000	1	1605 | 尾期 黑蓬頂 雙電門 雙暖座 USB插頭 DVDBT音響 泊...，YY Chung 電郵:js321@myyahoo.com | 寶馬 218iA GRAN TOURER	汽油	7座	1499cc	自動波	2018	$50,000	0	47</t>
+          <t>寶馬 335I COUPE	汽油	4座	3000cc	自動波	2008	$36,000	0	374 | 寶馬 118i M SPORT 116I	汽油	5座	1600cc	自動波	2013	$33,800	0	618 | 寶馬 316I	汽油	5座	1600cc	自動波	2013	$32,900	0	44</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>page_3_line_4841</t>
-        </is>
-      </c>
-      <c r="F14" t="n">
-        <v>3</v>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>2026-03-20 14:00:55</t>
+          <t>page_1_line_4976</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2026-04-01 07:00:19</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>62190476</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>js321@myyahoo.com</t>
-        </is>
-      </c>
+          <t>97604941</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr"/>
       <c r="C15" t="inlineStr">
         <is>
-          <t>寶馬 218iA GRAN TOURER 汽油 7座 1499cc 自動波 2018 $50,000 0 47</t>
+          <t>日產</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>任何 KAWASAKI ZX10R	汽油	2座	998cc	棍波	2006	$32,800	1	265 | 特斯拉 85D	電動	5座	158kW	自動波	2015	$108,000	0	2 | 豐田 VOXY HYBRID FACELIFT NOAH	混能	7座	1800cc	自動波	2021	$208,000	1	1605</t>
+          <t>寶馬 118i M SPORT 116I	汽油	5座	1600cc	自動波	2013	$33,800	0	618 | 寶馬 316I	汽油	5座	1600cc	自動波	2013	$32,900	0	44 | 寶馬 520D	柴油	5座	1995cc	自動波	2014	$78,000	1	80</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>page_3_line_4833</t>
-        </is>
-      </c>
-      <c r="F15" t="n">
-        <v>3</v>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>2026-03-20 14:00:55</t>
+          <t>page_1_line_4980</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2026-04-01 07:00:19</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>66172222</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>js321@myyahoo.com</t>
-        </is>
-      </c>
+          <t>98299002</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr"/>
       <c r="C16" t="inlineStr">
         <is>
-          <t>豐田 ALPHARD 3.5 汽油 7座 3500cc 自動波 2019 $279,000 0 1721</t>
+          <t>日產</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>凌志 NX300H	混能	5座	2494cc	自動波	2015	$82,000	1	607 | 豐田 ALPHARD 2.5 HYBRID SRC JBL	混能	7座	2500cc	自動波	2019	$368,888	1	1159 | 雙天窗 3電門 4電坐 前後冷暖坐 閱讀燈 JBL音響 後排...，YY Chung 電郵:js321@myyahoo.com</t>
+          <t>寶馬 316I	汽油	5座	1600cc	自動波	2013	$32,900	0	44 | 寶馬 520D	柴油	5座	1995cc	自動波	2014	$78,000	1	80 | 日產 NV350	柴油	5座	2488cc	棍波	2013	$65,000	2	3998</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>page_3_line_4869</t>
-        </is>
-      </c>
-      <c r="F16" t="n">
-        <v>3</v>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>2026-03-20 14:00:55</t>
+          <t>page_1_line_4984</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2026-04-01 07:00:19</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>90925106</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>js321@myyahoo.com</t>
-        </is>
-      </c>
+          <t>97404782</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr"/>
       <c r="C17" t="inlineStr">
         <is>
-          <t>奧迪 A3 SPORTBACK 35 TFSI SLINE 汽油 5座 1498cc 自動波 2021 $128,000 3 134</t>
+          <t>福士</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>豐田 ALPHARD 2.5 HYBRID SRC JBL	混能	7座	2500cc	自動波	2019	$368,888	1	1159 | 雙天窗 3電門 4電坐 前後冷暖坐 閱讀燈 JBL音響 後排...，YY Chung 電郵:js321@myyahoo.com | 五十鈴 PICK UP	柴油	5座	2499cc	自動波	2015	$93,000	2	1037</t>
+          <t>寶馬 520D	柴油	5座	1995cc	自動波	2014	$78,000	1	80 | 日產 NV350	柴油	5座	2488cc	棍波	2013	$65,000	2	3998 | 越野路華 VELAR R DYN SE P380	汽油	5座	2995cc	自動波	2018	$378,000	1	105</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>page_3_line_4873</t>
-        </is>
-      </c>
-      <c r="F17" t="n">
-        <v>3</v>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>2026-03-20 14:00:55</t>
+          <t>page_1_line_4988</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2026-04-01 07:00:19</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>91664985</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>js321@myyahoo.com</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr"/>
+          <t>94860547</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr"/>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>五十鈴</t>
+        </is>
+      </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>燃炓	座位	動力	傳動	年份	售價	留言	瀏覽	已售 | 任何 YAMAHA TMAX500	汽油	2座	499cc	自動波	2006	$18,800	1	2782 | 本田 CB190R	汽油	2座	184cc	棍波	2016	$15,800	1	2042</t>
+          <t>日產 NV350	柴油	5座	2488cc	棍波	2013	$65,000	2	3998 | 越野路華 VELAR R DYN SE P380	汽油	5座	2995cc	自動波	2018	$378,000	1	105 | 福士 EGOLF	電動	5座	100kW	自動波	2018	$52,000	1	343</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>page_3_line_4809</t>
-        </is>
-      </c>
-      <c r="F18" t="n">
-        <v>3</v>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>2026-03-20 14:00:55</t>
+          <t>page_1_line_4992</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026-04-01 07:00:19</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>46229124</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>georgeli9099@gmail.com</t>
-        </is>
-      </c>
+          <t>97476242</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr"/>
       <c r="C19" t="inlineStr">
         <is>
-          <t>豐田 ALPHARD 3.5 汽油 7座 3456cc 自動波 2016 $238,000 0 17</t>
+          <t>寶馬</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>富豪 XC90 T6 INSCRIPTION	汽油	7座	1969cc	自動波	2017	$168,000	0	2 | 豐田 LAND CRUISER 250 Prado VX	汽油	7座	2700cc	自動波	2025	$699,009	1	11138 | 25制 全新車 現貨 天窗 黑皮籠 冷暖電坐 前後恆溫 36...，Go 電郵:gogo28@myyahoo.com</t>
+          <t>燃炓	座位	動力	傳動	年份	售價	留言	瀏覽	已售 | 寶馬 320 GT FACELIFT	汽油	5座	1998cc	自動波	2018	$75,000	0	179 | 平治 E200 AVANTGARDE	汽油	5座	1991cc	自動波	2018	$88,500	0	290</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>page_4_line_4869</t>
-        </is>
-      </c>
-      <c r="F19" t="n">
-        <v>4</v>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>2026-03-20 14:01:05</t>
+          <t>page_1_line_4945</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026-03-31 11:12:47</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>62589888</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>js321@myyahoo.com</t>
-        </is>
-      </c>
+          <t>90839289</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr"/>
       <c r="C20" t="inlineStr">
         <is>
-          <t>豐田 ALPHARD 2.5 汽油 7座 2500cc 自動波 2023 $518,000 0 3</t>
+          <t>平治</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>豐田 VELLFIRE3.5	汽油	7座	3500cc	自動波	2014	$90,000	3	237 | 2014、汽油7座、5萬多公里、原版原漆、车况... (由於已售，聯絡人資料亦被保護中。) | 保時捷 MACAN 2.0	汽油	5座	2000cc	自動波	2015	$109,999	1	67</t>
+          <t>燃炓	座位	動力	傳動	年份	售價	留言	瀏覽	已售 | 寶馬 320 GT FACELIFT	汽油	5座	1998cc	自動波	2018	$75,000	0	179 | 平治 E200 AVANTGARDE	汽油	5座	1991cc	自動波	2018	$88,500	0	290</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>page_4_line_4841</t>
-        </is>
-      </c>
-      <c r="F20" t="n">
-        <v>4</v>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>2026-03-20 14:01:05</t>
+          <t>page_1_line_4949</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2026-03-31 11:12:47</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>65838610</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>georgeli9099@gmail.com</t>
-        </is>
-      </c>
+          <t>96888164</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr"/>
       <c r="C21" t="inlineStr">
         <is>
-          <t>豐田 LAND CRUISER 250 Prado VX 汽油 7座 2700cc 自動波 2025 $699,009 1 11138</t>
+          <t>凌志</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>豐田 PREIVA AERAS	汽油	7座	2400cc	自動波	2013	$57,999	1	10 | 行貨13製 牌費到七月中 實用家庭七座位 重心低 3電門 雙...，HO LUN YING 電郵:georgeli9099@gmail.com | 富豪 XC90 T6 INSCRIPTION	汽油	7座	1969cc	自動波	2017	$168,000	0	2</t>
+          <t>燃炓	座位	動力	傳動	年份	售價	留言	瀏覽	已售 | 寶馬 320 GT FACELIFT	汽油	5座	1998cc	自動波	2018	$75,000	0	179 | 平治 E200 AVANTGARDE	汽油	5座	1991cc	自動波	2018	$88,500	0	290</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>page_4_line_4865</t>
-        </is>
-      </c>
-      <c r="F21" t="n">
-        <v>4</v>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>2026-03-20 14:01:05</t>
+          <t>page_1_line_4953</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2026-03-31 11:12:47</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>67262528</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>georgeli9099@gmail.com</t>
-        </is>
-      </c>
+          <t>55051388</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr"/>
       <c r="C22" t="inlineStr">
         <is>
-          <t>富豪 XC90 T6 INSCRIPTION 汽油 7座 1969cc 自動波 2017 $168,000 0 2</t>
+          <t>保時捷</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t xml:space="preserve">豐田 VELLFIRE 2.5 ALPHARD	汽油	7座	2500cc	自動波	2021	$267,990	1	155 | 20落地 1字 6萬km 中凳大班椅 雙天窗 中排吊螢幕 3...，HO LUN YING 電郵:georgeli9099@gmail.com | 豐田 SIENTA HYBRID G MODELLISTA	混能	7座	1500cc	自動波	2018	$118,000	1	</t>
+          <t>平治 230SL PAGODA	汽油	2座	2300cc	自動波	1966	$1,200,001	1	3546 | 保時捷 MACAN S	汽油	5座	3000cc	自動波	2017	$148,001	0	522 | 豐田 ALPHARD 250	汽油	7座	2500cc	自動波	2023	$628,001	1	388</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>page_4_line_4857</t>
-        </is>
-      </c>
-      <c r="F22" t="n">
-        <v>4</v>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>2026-03-20 14:01:05</t>
+          <t>page_1_line_4969</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2026-03-31 11:12:47</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>94856084</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>js321@myyahoo.com</t>
-        </is>
-      </c>
+          <t>51343578</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr"/>
       <c r="C23" t="inlineStr">
         <is>
-          <t>凌志 UX200 ULTIMATE 混能 5座 2000cc 自動波 2020 $108,000 0 2</t>
+          <t>豐田</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>豐田 YARIS HYBRID Z MODELLISTA	混能	5座	1500cc	自動波	2021	$148,000	1	2491 | Z版 黑籠 雙暖座 CarPlay音響 360鏡頭 前後感應...，YY Chung 電郵:js321@myyahoo.com | 豐田 VELLFIRE3.5	汽油	7座	3500cc	自動波	2014	$90,000	3	237</t>
+          <t>平治 C63S AMG	汽油	5座	4000cc	自動波	2016	$228,000	1	1556 | 勞斯萊斯 PHANTOM EWB SERIES II	汽油	4座	6749cc	自動波	2024	$8,300,000	1	453 | 平治 C63S AMG	汽油	5座	4000cc	自動波	2016	$228,000	0	1283</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>page_4_line_4837</t>
-        </is>
-      </c>
-      <c r="F23" t="n">
-        <v>4</v>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>2026-03-20 14:01:05</t>
+          <t>page_1_line_5017</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2026-03-31 11:12:47</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>53218551</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>js66@myyahoo.com</t>
-        </is>
-      </c>
+          <t>91362339</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr"/>
       <c r="C24" t="inlineStr">
         <is>
-          <t>萬事得 CX9 汽油 7座 2500cc 自動波 2019 $108,000 0 16</t>
+          <t>豐田</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>本田 FREED HYBRID	混能	7座	1496cc	自動波	2017	$87,888	1	1162 | 豐田 VELLFIRE 3.5 WELCAB	汽油	7座	3500cc	自動波	2016	$188,000	1	770 | 豐田 ESQUIRE HYBRID GI	混能	7座	1800cc	自動波	2019	$198,888	1	2465</t>
+          <t>勞斯萊斯 PHANTOM EWB SERIES II	汽油	4座	6749cc	自動波	2024	$8,300,000	1	453 | 平治 C63S AMG	汽油	5座	4000cc	自動波	2016	$228,000	0	1283 | 豐田 FIELDER HYBRID WXB FACELIFT	混能	5座	1500cc	自動波	2017	$85,001	0	459</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>page_5_line_4853</t>
-        </is>
-      </c>
-      <c r="F24" t="n">
-        <v>5</v>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>2026-03-20 14:01:15</t>
+          <t>page_1_line_5021</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2026-03-31 11:12:47</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>59655535</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>georgeli9099@gmail.com</t>
-        </is>
-      </c>
+          <t>98395961</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr"/>
       <c r="C25" t="inlineStr">
         <is>
-          <t>豐田 ALPHARD 3.5 汽油 7座 3456cc 自動波 2017 $238,000 0 161</t>
+          <t>日產</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>燃炓	座位	動力	傳動	年份	售價	留言	瀏覽	已售 | 豐田 SPADE 1.5	汽油	5座	1500cc	自動波	2012	$38,000	1	60 | 行貨1字 7萬9公里 趟門上落方便 空間闊落 360泊車 內...，HO LUN YING 電郵:georgeli9099@gmail.com</t>
+          <t>燃炓	座位	動力	傳動	年份	售價	留言	瀏覽	已售 | 日產 NV350	柴油	6座	2488cc	自動波	2017	$93,000	0	324 | 保時捷 911 Turbo 996	汽油	4座	3600cc	棍波	2001	$447,000	0	5007</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>page_5_line_4817</t>
-        </is>
-      </c>
-      <c r="F25" t="n">
-        <v>5</v>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>2026-03-20 14:01:15</t>
+          <t>page_1_line_4945</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2026-03-31 11:09:08</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>92220890</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>js66@myyahoo.com</t>
-        </is>
-      </c>
+          <t>92881202</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr"/>
       <c r="C26" t="inlineStr">
         <is>
-          <t>豐田 GR86 RC 汽油 4座 2400cc 棍波 2025 $318,000 1 9320</t>
+          <t>保時捷</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>豐田 VELLFIRE 2.5 ALPHARD	汽油	8座	2498cc	自動波	2015	$147,888	1	539 | 豐田 GR86 RC	汽油	4座	2400cc	棍波	2025	$318,000	1	9320 | 25制 白色 全新車 現貨 改良款 Eyesight系統 泊...，RR CHAN 電郵:js66@myyahoo.com</t>
+          <t>燃炓	座位	動力	傳動	年份	售價	留言	瀏覽	已售 | 日產 NV350	柴油	6座	2488cc	自動波	2017	$93,000	0	324 | 保時捷 911 Turbo 996	汽油	4座	3600cc	棍波	2001	$447,000	0	5007</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>page_5_line_4873</t>
-        </is>
-      </c>
-      <c r="F26" t="n">
-        <v>5</v>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>2026-03-20 14:01:15</t>
+          <t>page_1_line_4949</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2026-03-31 11:09:08</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>98751864</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>georgeli9099@gmail.com</t>
-        </is>
-      </c>
+          <t>70148961</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr"/>
       <c r="C27" t="inlineStr">
         <is>
-          <t>本田 SHUTTLE HYBRID GP7 混能 5座 1496cc 自動波 2015 $60,000 1 522</t>
+          <t>寶馬</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>豐田 ALPHARD 3.5	汽油	7座	3456cc	自動波	2017	$238,000	0	161 | 豐田 ALPHARD 2.5 Z	汽油	7座	2500cc	自動波	2025	$578,000	1	701 | 豐田 HIACE	柴油	6座	2755cc	自動波	2022	$238,000	0	218</t>
+          <t>燃炓	座位	動力	傳動	年份	售價	留言	瀏覽	已售 | 日產 NV350	柴油	6座	2488cc	自動波	2017	$93,000	0	324 | 保時捷 911 Turbo 996	汽油	4座	3600cc	棍波	2001	$447,000	0	5007</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>page_5_line_4829</t>
-        </is>
-      </c>
-      <c r="F27" t="n">
-        <v>5</v>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>2026-03-20 14:01:15</t>
+          <t>page_1_line_4957</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2026-03-31 11:09:08</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>63453124</t>
+          <t>92861361</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>ying89614@gmail.com</t>
+          <t>bokhom1220@gmail.com</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>豐田 VELLFIRE 2.5 汽油 8座 2500cc 自動波 2015 $138,001 0 1672</t>
+          <t>賓利</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>平治 GLC250 4MATIC AMG	汽油	5座	2000cc	自動波	2018	$118,001	0	44 | 保時捷 CAYMAN S	汽油	2座	3400cc	自動波	2006	$79,000	0	371 | 本田 FREED HYBRID GB7	混能	6座	1500cc	自動波	2020	$122,000	1	2893</t>
+          <t>寶馬 120i M SPORT	汽油	5座	1998cc	自動波	2021	$138,000	0	0 | 本田 FK2 TYPE R	汽油	5座	2000cc	棍波	2016	$199,999	0	4472 | 豐田 Supra A80 AERO TOP	汽油	4座	3000cc	棍波	1993	$527,000	0	5471</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>page_6_line_4853</t>
-        </is>
-      </c>
-      <c r="F28" t="n">
-        <v>6</v>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>2026-03-20 14:01:24</t>
+          <t>page_1_line_4969</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>2026-03-31 11:09:08</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>90880900</t>
+          <t>93095474</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>ying89614@gmail.com</t>
+          <t>bokhom1220@gmail.com</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>保時捷 CAYMAN S 汽油 2座 3400cc 自動波 2006 $79,000 0 371</t>
+          <t>賓利</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>豐田 VELLFIRE 2.5 ZG	汽油	7座	2500cc	自動波	2017	$228,008	1	697 | 豐田 VELLFIRE 3.5 ZG JBL	汽油	7座	3500cc	自動波	2019	$348,000	1	405 | 黑色 雙天窗 3電門 4電坐 冷暖坐 空氣淨化 JBL音響 ...，JS 電郵:js17@myyahoo.com</t>
+          <t>本田 FK2 TYPE R	汽油	5座	2000cc	棍波	2016	$199,999	0	4472 | 豐田 Supra A80 AERO TOP	汽油	4座	3000cc	棍波	1993	$527,000	0	5471 | 賓利 ARNAGE T	汽油	4座	6750cc	自動波	2009	$488,000	1	592</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>page_6_line_4845</t>
-        </is>
-      </c>
-      <c r="F29" t="n">
-        <v>6</v>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>2026-03-20 14:01:24</t>
+          <t>page_1_line_4973</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2026-03-31 11:09:08</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>94616278</t>
+          <t>68898681</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>js17@myyahoo.com</t>
+          <t>bokhom1220@gmail.com</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>豐田 Previa AERAS 汽油 7座 2362cc 自動波 2014 $49,000 0 1095</t>
+          <t>豐田</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>豐田 VELLFIRE 2.5	汽油	8座	2500cc	自動波	2015	$138,001	0	1672 | 豐田 PRIUS 1.8 HYBRID	混能	5座	1800cc	自動波	2019	$128,888	1	3203 | 白色黑頂 Keyless 恆溫冷氣 DVD BT音響 泊車鏡...，JS 電郵:js17@myyahoo.com</t>
+          <t>豐田 Supra A80 AERO TOP	汽油	4座	3000cc	棍波	1993	$527,000	0	5471 | 賓利 ARNAGE T	汽油	4座	6750cc	自動波	2009	$488,000	1	592 | 任何 SYM TL500 I ABS	汽油	2座	465cc	棍波	2020	$17,000	2	81</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>page_6_line_4865</t>
-        </is>
-      </c>
-      <c r="F30" t="n">
-        <v>6</v>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>2026-03-20 14:01:24</t>
+          <t>page_1_line_4977</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>2026-03-31 11:09:08</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>59663109</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr"/>
+          <t>51337644</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>bokhom1220@gmail.com</t>
+        </is>
+      </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>快意 ABARTH 595C 汽油 4座 1368cc 自動波 2013 $75,000 0 4</t>
+          <t>豐田</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>燃炓	座位	動力	傳動	年份	售價	留言	瀏覽	已售 | 寶馬 318iA SALOON SPORT	汽油	5座	2000cc	自動波	2021	$132,000	1	2886 | 豐田 NOAH 1.8 HYBRID	混能	7座	1800cc	自動波	2018	$163,000	1	821</t>
+          <t>賓利 ARNAGE T	汽油	4座	6750cc	自動波	2009	$488,000	1	592 | 任何 SYM TL500 I ABS	汽油	2座	465cc	棍波	2020	$17,000	2	81 | 豐田 PORTE	汽油	5座	1500cc	自動波	2015	$49,800	0	2781</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>page_7_line_4821</t>
-        </is>
-      </c>
-      <c r="F31" t="n">
-        <v>7</v>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>2026-03-20 14:01:35</t>
+          <t>page_1_line_4981</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>2026-03-31 11:09:08</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>66382688</t>
+          <t>64642601</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>yoyo168@myyahoo.com</t>
+          <t>bokhom1220@gmail.com</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>迷你 MINI Cooper 汽油 5座 1490cc 自動波 2019 $86,000 1 405</t>
+          <t>萬事得</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>豐田 ALPHARD 2.5 HYBRID HEV	混能	7座	2500cc	自動波	2023	$688,008	1	948 | 豐田 VELLFIRE 2.5 HYBRID	混能	7座	2493cc	自動波	2024	$678,800	0	394 | 豐田 VELLFIRE EXECUTIVE LOUNGE	汽油	7座	2493cc	自動波	2024	$788,800	0	315</t>
+          <t>豐田 PORTE	汽油	5座	1500cc	自動波	2015	$49,800	0	2781 | 任何 HARLEY DAVIDSON NIGHTSTER SPEC	汽油	2座	975cc	棍波	2023	$140,500	2	1783 | 豐田 Previa	汽油	7座	2500cc	自動波	2018	$130,000	0	2345</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>page_7_line_4841</t>
-        </is>
-      </c>
-      <c r="F32" t="n">
-        <v>7</v>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>2026-03-20 14:01:35</t>
+          <t>page_1_line_4989</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>2026-03-31 11:09:08</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>68211289</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr"/>
+          <t>94523594</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>bokhom1220@gmail.com</t>
+        </is>
+      </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>豐田 ALPHARD EXECUTIVE LOUNGE 汽油 7座 3456cc 自動波 2020 $368,800 0 384</t>
+          <t>平治</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>燃炓	座位	動力	傳動	年份	售價	留言	瀏覽	已售 | 寶馬 318iA SALOON SPORT	汽油	5座	2000cc	自動波	2021	$132,000	1	2886 | 豐田 NOAH 1.8 HYBRID	混能	7座	1800cc	自動波	2018	$163,000	1	821</t>
+          <t>本田 FIT HYBRID	混能	5座	1500cc	自動波	2017	$63,900	2	327 | 平治 CLA250 AMG	汽油	5座	1991cc	自動波	2015	$68,000	1	132 | 2015制、白色、半皮籠、天窗、ANDROID車機、包圍、1...，Hom 電郵:bokhom1220@gmail.com</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>page_7_line_4817</t>
-        </is>
-      </c>
-      <c r="F33" t="n">
-        <v>7</v>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>2026-03-20 14:01:35</t>
+          <t>page_1_line_5017</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>2026-03-31 11:09:08</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>97902449</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>yusonyuson79@gmail.com</t>
-        </is>
-      </c>
+          <t>61259683</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr"/>
       <c r="C34" t="inlineStr">
         <is>
-          <t>豐田 Previa DELUXE 汽油 8座 2400cc 自動波 2014 $59,000 1 766</t>
+          <t>鈴木</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>豐田 VELLFIRE 2.5 FACELIFT ALPHARD	汽油	7座	2500cc	自動波	2020	$258,001	1	6856 | 同場多架現貨、未出牌、四電動記憶中櫈、三電動門...，Yuson 電郵:yusonyuson79@gmail.com | 豐田 VOXY HYBRID NOAH	混能	7座	1800cc	自動波	2018	$117,801	1	2934</t>
+          <t>燃炓	座位	動力	傳動	年份	售價	留言	瀏覽	已售 | 鈴木 Jimny XL	汽油	4座	1460cc	自動波	2025	$258,000	1	687 | 豐田 RAV4 DELUXE	汽油	5座	1987cc	自動波	2021	$158,000	1	631</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>page_8_line_4869</t>
-        </is>
-      </c>
-      <c r="F34" t="n">
-        <v>8</v>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>2026-03-20 14:01:44</t>
+          <t>page_1_line_4943</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>2026-03-31 08:00:19</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>53074323</t>
+          <t>98893576</t>
         </is>
       </c>
       <c r="B35" t="inlineStr"/>
       <c r="C35" t="inlineStr">
         <is>
-          <t>豐田 VOXY HYBRID ZS FACELIFT 混能 7座 1800cc 自動波 2019 $178,000 0 4</t>
+          <t>五十鈴</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>豐田 VELLFIRE 3.5 ZG FACELIFT	汽油	7座	3500cc	自動波	2020	$318,001	1	3345 | 富士 FORESTER 2.0XT	汽油	5座	2000cc	自動波	2015	$48,008	0	1289 | 豐田 VELLFIRE 2.5 FACELIFT ALPHARD	汽油	7座	2500cc	自動波	2019	$248,001	0	3497</t>
+          <t>燃炓	座位	動力	傳動	年份	售價	留言	瀏覽	已售 | 鈴木 Jimny XL	汽油	4座	1460cc	自動波	2025	$258,000	1	687 | 豐田 RAV4 DELUXE	汽油	5座	1987cc	自動波	2021	$158,000	1	631</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>page_9_line_4873</t>
-        </is>
-      </c>
-      <c r="F35" t="n">
-        <v>9</v>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>2026-03-20 14:01:54</t>
+          <t>page_1_line_4951</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>2026-03-31 08:00:19</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>53601171</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr"/>
+          <t>92267908</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>jimmywai@myyahoo.com</t>
+        </is>
+      </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>奧迪 A5 40TFSI SLINE AVANT 汽油 5座 2000cc 自動波 2025 $458,001 1 893</t>
+          <t>福特</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>豐田 VELLFIRE 2.5 FACELIFT ALPHARD	汽油	7座	2500cc	自動波	2019	$248,001	0	3497 | 豐田 VOXY HYBRID ZS FACELIFT	混能	7座	1800cc	自動波	2019	$178,000	0	4 | 日野 500	柴油	3座	7684cc	棍波	2013	$240,000	0	54</t>
+          <t>起亞 SORENTO GT PLATINUM	汽油	6座	2497cc	自動波	2021	$158,000	1	262 | 五十鈴 N	柴油	5座	5193cc	棍波	2022	$299,500	0	174 | 五十鈴 NQR 9TON	柴油	2座	5193cc	棍波	2017	$215,800	1	290</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>page_9_line_4881</t>
-        </is>
-      </c>
-      <c r="F36" t="n">
-        <v>9</v>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>2026-03-20 14:01:54</t>
+          <t>page_1_line_4967</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>2026-03-31 08:00:19</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>53937499</t>
+          <t>46230177</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>bubu666999111@gmail.com</t>
+          <t>jimmywai@myyahoo.com</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>豐田 HIACE 300 柴油 5座 2755cc 自動波 2022 $265,000 0 2</t>
+          <t>豐田</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>燃炓	座位	動力	傳動	年份	售價	留言	瀏覽	已售 | 本田 STEPWGN HYBRID RP5	混能	7座	2000cc	自動波	2022	$188,000	1	2160 | 豐田 HIACE 300	柴油	5座	2755cc	自動波	2022	$265,000	0	2</t>
+          <t>福特 FOCUS ST	汽油	5座	1999cc	棍波	2013	$68,800	1	609 | 本田 JAZZ GK5 RS	汽油	5座	1496cc	自動波	2020	$108,000	0	439 | 豐田 VELLFIRE 2.5 FACELIFT	汽油	7座	2500cc	自動波	2016	$158,000	0	3538</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>page_9_line_4813</t>
-        </is>
-      </c>
-      <c r="F37" t="n">
-        <v>9</v>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>2026-03-20 14:01:54</t>
+          <t>page_1_line_4979</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>2026-03-31 08:00:19</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>60722845</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr"/>
+          <t>92669392</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>jimmywai@myyahoo.com</t>
+        </is>
+      </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>豐田 ALPHARD 3.5 汽油 7座 3456cc 自動波 2009 $48,000 0 78</t>
+          <t>豐田</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>豐田 VOXY HYBRID ZS FACELIFT	混能	7座	1800cc	自動波	2019	$178,000	0	4 | 日野 500	柴油	3座	7684cc	棍波	2013	$240,000	0	54 | 車斗3米8、27尺長、13年 16ton 無死期 (由於已售，聯絡人資料亦被保護中。)</t>
+          <t>豐田 VOXY HYBRID SZ NOAH	混能	7座	1800cc	自動波	2016	$90,001	0	4554 | 豐田 VOXY HYBRID ZS FACELIFT NOAH	混能	7座	1800cc	自動波	2016	$90,000	3	3370 | 多架油電七座現貨、未出牌、HYBRID油電引擎、遙控雙電趟門...，Jimmy 電郵:jimmywai@myyahoo.com</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>page_9_line_4885</t>
-        </is>
-      </c>
-      <c r="F38" t="n">
-        <v>9</v>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>2026-03-20 14:01:54</t>
+          <t>page_1_line_4991</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>2026-03-31 08:00:19</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>61276373</t>
+          <t>56194055</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>bubu666999111@gmail.com</t>
+          <t>jimmywai@myyahoo.com</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>寶馬 X3 20i FACELIFT 汽油 5座 1998cc 自動波 2022 $259,000 1 922</t>
+          <t>本田</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>寶馬 X3 XDRIVE20iA XLINE	汽油	5座	1998cc	自動波	2018	$98,000	0	1273 | 豐田 VELLFIRE 2.5 FACELIFT	汽油	7座	2500cc	自動波	2016	$158,000	0	3215 | 豐田 VELLFIRE 2.5 FACELIFT	汽油	7座	2500cc	自動波	2018	$178,001	0	2462</t>
+          <t>豐田 VOXY HYBRID ZS FACELIFT NOAH	混能	7座	1800cc	自動波	2016	$90,000	3	3370 | 多架油電七座現貨、未出牌、HYBRID油電引擎、遙控雙電趟門...，Jimmy 電郵:jimmywai@myyahoo.com | 豐田 VELLFIRE 2.5 FACELIFT ALPHARD	汽油	7座	2500cc	自動波	2016	$178,001</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>page_9_line_4857</t>
-        </is>
-      </c>
-      <c r="F39" t="n">
-        <v>9</v>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>2026-03-20 14:01:54</t>
+          <t>page_1_line_4995</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>2026-03-31 08:00:19</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>66699911</t>
+          <t>51708296</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>bubu666999111@gmail.com</t>
+          <t>jimmywai@myyahoo.com</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>豐田 VOXY HYBRID NOAH 汽油 7座 1800cc 自動波 2015 $88,001 1 2091</t>
+          <t>平治</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>日產 FAIRLADY Z33 350Z	汽油	2座	3498cc	棍波	2003	$45,000	0	2415 | 車爽、good handling、保養佳、內外新淨、手數高、... (由於已售，聯絡人資料亦被保護中。) | 起亞 SORENTO	汽油	7座	2400cc	自動波	2015	$55,000	1	245</t>
+          <t>豐田 VELLFIRE 2.5 FACELIFT ALPHARD	汽油	7座	2500cc	自動波	2016	$178,001	0	5333 | 豐田 PRIUS 1.8 HYBRID GS	混能	5座	1987cc	自動波	2012	$38,000	0	2 | 本田 JAZZ GE6	汽油	5座	1339cc	自動波	2013	$32,000	1	312</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>page_9_line_4829</t>
-        </is>
-      </c>
-      <c r="F40" t="n">
-        <v>9</v>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>2026-03-20 14:01:54</t>
+          <t>page_1_line_4999</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>2026-03-31 08:00:19</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>91498709</t>
+          <t>63956394</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>bubu666999111@gmail.com</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>寶馬 220iA ACTIVE TOURER 汽油 5座 1998cc 自動波 2015 $40,008 0 1995</t>
-        </is>
-      </c>
+          <t>magchan2221@gmail.com</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr"/>
       <c r="D41" t="inlineStr">
         <is>
-          <t>豐田 HIACE 300	柴油	5座	2755cc	自動波	2022	$265,000	0	2 | 日產 FAIRLADY Z33 350Z	汽油	2座	3498cc	棍波	2003	$45,000	0	2415 | 車爽、good handling、保養佳、內外新淨、手數高、... (由於已售，聯絡人資料亦被保護中。)</t>
+          <t>燃炓	座位	動力	傳動	年份	售價	留言	瀏覽	已售 | 任何 001FR	電動	5座	151kW	自動波	2025	$668,000	0	626 | 三菱 ECLIPSE CROSS	汽油	5座	1500cc	自動波	2018	$68,001	0	4116</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>page_9_line_4825</t>
-        </is>
-      </c>
-      <c r="F41" t="n">
-        <v>9</v>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>2026-03-20 14:01:54</t>
+          <t>page_1_line_4943</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>2026-03-31 02:00:26</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>93793325</t>
+          <t>93612617</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>bubu666999111@gmail.com</t>
+          <t>magchan2221@gmail.com</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>豐田 VOXY HYBRID ZS FACELIFT NOAH 混能 7座 1800cc 自動波 2015 $88,001 0 8252</t>
+          <t>三菱</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>豐田 VOXY HYBRID NOAH	汽油	7座	1800cc	自動波	2015	$88,001	1	2091 | 未出牌🚗 keyless 頂級版 皮座 正廠...，Lam 電郵:bubu666999111@gmail.com | 凌志 CT200H F SPORT	混能	5座	1798cc	自動波	2012	$45,008	1	2881</t>
+          <t>燃炓	座位	動力	傳動	年份	售價	留言	瀏覽	已售 | 任何 001FR	電動	5座	151kW	自動波	2025	$668,000	0	626 | 三菱 ECLIPSE CROSS	汽油	5座	1500cc	自動波	2018	$68,001	0	4116</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>page_9_line_4841</t>
-        </is>
-      </c>
-      <c r="F42" t="n">
-        <v>9</v>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>2026-03-20 14:01:54</t>
+          <t>page_1_line_4947</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>2026-03-31 02:00:26</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>61997777</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr"/>
+          <t>63836120</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>magchan2221@gmail.com</t>
+        </is>
+      </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>寶馬 430iA COUPE M SPORT EDITION 汽油 4座 2000cc 自動波 2019 $156,001 1 266</t>
+          <t>豐田</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>平治 S400 HYBRID	汽油	5座	3498cc	自動波	2014	$158,000	0	719 | 豐田 VELLFIRE 2.4 Turbo Z PREMIER	汽油	7座	2400cc	自動波	2026	$858,000	1	204 | 寶馬 430iA COUPE M SPORT EDITION	汽油	4座	2000cc	自動波	2019	$156,001	1	266</t>
+          <t>燃炓	座位	動力	傳動	年份	售價	留言	瀏覽	已售 | 任何 001FR	電動	5座	151kW	自動波	2025	$668,000	0	626 | 三菱 ECLIPSE CROSS	汽油	5座	1500cc	自動波	2018	$68,001	0	4116</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>page_10_line_4881</t>
-        </is>
-      </c>
-      <c r="F43" t="n">
-        <v>10</v>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>2026-03-20 14:02:04</t>
+          <t>page_1_line_4951</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>2026-03-31 02:00:26</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>98549548</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr"/>
+          <t>98247180</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>magchan2221@gmail.com</t>
+        </is>
+      </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>起亞 SORENTO DIESEL 柴油 5座 2200cc 自動波 2019 $64,000 3 368</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>豐田 ALPHARD 2.5 Z	汽油	7座	2500cc	自動波	2026	$698,001	1	357 | 豐田 ALPHARD 3.5 GF	汽油	7座	3500cc	自動波	2018	$298,000	1	1006 | 豐田 ALPHARD 2.5 Z	汽油	7座	2500cc	自動波	2025	$668,000	1	740</t>
+          <t>燃炓	座位	動力	傳動	年份	售價	留言	瀏覽	已售 | 任何 001FR	電動	5座	151kW	自動波	2025	$668,000	0	626 | 三菱 ECLIPSE CROSS	汽油	5座	1500cc	自動波	2018	$68,001	0	4116</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>page_10_line_4837</t>
-        </is>
-      </c>
-      <c r="F44" t="n">
-        <v>10</v>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>2026-03-20 14:02:04</t>
+          <t>page_1_line_4955</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>2026-03-31 02:00:26</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>98886669</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr"/>
+          <t>69365040</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>magchan2221@gmail.com</t>
+        </is>
+      </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>豐田 ALPHARD 2.5Z 汽油 7座 2493cc 自動波 2026 $668,000 0 319</t>
+          <t>奧迪</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>平治 GLA200 AMG FACELIFT	汽油	5座	2000cc	自動波	2019	$95,801	1	155 | 任何 GAC HYPTEC HT ULTRA PLUS	電動	5座	83kW	自動波	2026	$299,000	1	288 | 本田 CRV 1.5 Turbo	汽油	7座	1500cc	自動波	2025	$285,000	1	1080</t>
+          <t>三菱 ECLIPSE CROSS	汽油	5座	1500cc	自動波	2018	$68,001	0	4116 | 豐田 VELLFIRE 2.5 FACELIFT	汽油	7座	2500cc	自動波	2018	$238,000	0	1 | 特斯拉 MODEL S P90D	電動	5座	169kW	自動波	2015	$133,000	3	559</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>page_10_line_4865</t>
-        </is>
-      </c>
-      <c r="F45" t="n">
-        <v>10</v>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>2026-03-20 14:02:04</t>
+          <t>page_1_line_4959</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>2026-03-31 02:00:26</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>56266366</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr"/>
+          <t>98028868</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>magchan2221@gmail.com</t>
+        </is>
+      </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>豐田 ALPHARD 2.5Z 汽油 7座 2493cc 自動波 2023 $528,008 0 734</t>
+          <t>平治</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>燃炓	座位	動力	傳動	年份	售價	留言	瀏覽	已售 | 奧迪 Q7 40 TFSI QUATTRO	汽油	7座	2000cc	自動波	2019	$148,000	1	187 | 迷你 MINI Cooper COUNTRYMAN	汽油	5座	1598cc	自動波	2016	$58,001	1	98</t>
+          <t>特斯拉 MODEL S P90D	電動	5座	169kW	自動波	2015	$133,000	3	559 | 奧迪 A3 1.4T SEDAN	汽油	5座	1400cc	自動波	2016	$47,000	1	202 | 豐田 ALPHARD 2.5 SC MODELLISTA	汽油	7座	2500cc	自動波	2021	$308,000	1	11</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>page_11_line_4817</t>
-        </is>
-      </c>
-      <c r="F46" t="n">
-        <v>11</v>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>2026-03-20 14:02:14</t>
+          <t>page_1_line_4967</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>2026-03-31 02:00:26</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>61112699</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr"/>
+          <t>34814222</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>magchan2221@gmail.com</t>
+        </is>
+      </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>保時捷 911 CARRERA 2S 991.2 汽油 4座 3000cc 自動波 2016 $997,999 0 137</t>
+          <t>平治</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>豐田 ALPHARD 2.5Z	汽油	7座	2493cc	自動波	2023	$528,008	0	734 | 豐田 ALPHARD 3.5 GF	汽油	7座	3500cc	自動波	2015	$178,000	1	43 | 豐田 ALPHARD 3.5 EXECUTIVE LOUNGE	汽油	7座	3500cc	自動波	2020	$378,001	1	164</t>
+          <t>奧迪 A3 1.4T SEDAN	汽油	5座	1400cc	自動波	2016	$47,000	1	202 | 豐田 ALPHARD 2.5 SC MODELLISTA	汽油	7座	2500cc	自動波	2021	$308,000	1	11 | 尾期 雙天窗 3電門 4電座 JBL 360鏡頭 CARPL...，Mag 電郵:magchan2221@gmail.com</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>page_11_line_4829</t>
-        </is>
-      </c>
-      <c r="F47" t="n">
-        <v>11</v>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>2026-03-20 14:02:14</t>
+          <t>page_1_line_4971</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>2026-03-31 02:00:26</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>61123032</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr"/>
+          <t>52642941</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>ws34814222@yahoo.com</t>
+        </is>
+      </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>豐田 VOXY HYBRID ZS FACELIFT NOAH 混能 7座 1800cc 自動波 2016 $90,001 1 4085</t>
+          <t>奧迪</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>本田 FD2 TYPE R	汽油	4座	1998cc	棍波	2009	$159,000	1	6149 | 法拉利 CALIFORNIA T	汽油	5座	3800cc	自動波	2015	$947,999	0	241 | 特斯拉 MODEL 3 SR PLUS	電動	5座	88kW	自動波	2019	$89,000	0	147</t>
+          <t>任何 DRG	汽油	2座	158cc	自動波	2020	$20,000	1	74 | 己做全車檢查.售後保用1個月，ws 電郵:ws34814222@yahoo.com | 任何 ADV150	汽油	2座	150cc	自動波	2020	$17,000	1	183</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>page_11_line_4881</t>
-        </is>
-      </c>
-      <c r="F48" t="n">
-        <v>11</v>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>2026-03-20 14:02:14</t>
+          <t>page_1_line_4995</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>2026-03-31 02:00:26</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>91312375</t>
+          <t>91985815</t>
         </is>
       </c>
       <c r="B49" t="inlineStr"/>
       <c r="C49" t="inlineStr">
         <is>
-          <t>本田 NSX NC1 汽油 2座 3493cc 自動波 2016 $2,279,999 1 2785</t>
+          <t>起亞 SORENTO DIESEL V2.2 汽油 5座 2199cc 自動波 2018 $73,800 0 91</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>保時捷 911 CARRERA 2S 991.2	汽油	4座	3000cc	自動波	2016	$997,999	0	137 | 起亞 SORENTO DIESEL	柴油	7座	2200cc	自動波	2017	$119,000	1	6622 | 本田 NSX NC1	汽油	2座	3493cc	自動波	2016	$2,279,999	1	2785</t>
+          <t>燃炓	座位	動力	傳動	年份	售價	留言	瀏覽	已售 | 起亞 SORENTO DIESEL V2.2	汽油	5座	2199cc	自動波	2018	$73,800	0	91 | 寶馬 X5 XDRIVE30D	柴油	7座	2993cc	自動波	2014	$130,000	1	719</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>page_11_line_4841</t>
-        </is>
-      </c>
-      <c r="F49" t="n">
-        <v>11</v>
-      </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>2026-03-20 14:02:14</t>
+          <t>page_1_line_4933</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>2026-03-30 12:18:24</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>98660834</t>
+          <t>92724670</t>
         </is>
       </c>
       <c r="B50" t="inlineStr"/>
       <c r="C50" t="inlineStr">
         <is>
-          <t>特斯拉 MODEL 3 SR PLUS 電動 5座 88kW 自動波 2019 $89,000 0 147</t>
+          <t>寶馬 X5 XDRIVE30D 柴油 7座 2993cc 自動波 2014 $130,000 1 719</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>豐田 PRIUS 1.8 HYBRID	混能	5座	1800cc	自動波	2013	$33,800	1	2309 | 本田 FD2 TYPE R	汽油	4座	1998cc	棍波	2009	$159,000	1	6149 | 法拉利 CALIFORNIA T	汽油	5座	3800cc	自動波	2015	$947,999	0	241</t>
+          <t>燃炓	座位	動力	傳動	年份	售價	留言	瀏覽	已售 | 起亞 SORENTO DIESEL V2.2	汽油	5座	2199cc	自動波	2018	$73,800	0	91 | 寶馬 X5 XDRIVE30D	柴油	7座	2993cc	自動波	2014	$130,000	1	719</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>page_11_line_4877</t>
-        </is>
-      </c>
-      <c r="F50" t="n">
-        <v>11</v>
-      </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>2026-03-20 14:02:14</t>
+          <t>page_1_line_4937</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>2026-03-30 12:18:24</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>98889889</t>
+          <t>97678100</t>
         </is>
       </c>
       <c r="B51" t="inlineStr"/>
       <c r="C51" t="inlineStr">
         <is>
-          <t>起亞 SORENTO DIESEL 柴油 7座 2200cc 自動波 2017 $119,000 1 6622</t>
+          <t>雷諾 MEGANE RS250 MK3 MONACO GP 汽油 5座 2000cc 棍波 2011 $55,001 0 7713</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>豐田 ALPHARD 3.5 GF	汽油	7座	3500cc	自動波	2015	$178,000	1	43 | 豐田 ALPHARD 3.5 EXECUTIVE LOUNGE	汽油	7座	3500cc	自動波	2020	$378,001	1	164 | 保時捷 911 CARRERA 2S 991.2	汽油	4座	3000cc	自動波	2016	$997,999	0	137</t>
+          <t>寶馬 X5 XDRIVE30D	柴油	7座	2993cc	自動波	2014	$130,000	1	719 | 豐田 ALPHARD 2.5 Z	汽油	7座	2500cc	自動波	2025	$638,008	0	838 | 寶馬 X7 XDRIVE 50M SPORT	汽油	6座	4400cc	自動波	2019	$748,000	0	237</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>page_11_line_4833</t>
-        </is>
-      </c>
-      <c r="F51" t="n">
-        <v>11</v>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>2026-03-20 14:02:14</t>
+          <t>page_1_line_4949</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>2026-03-30 12:18:24</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>27082922</t>
+          <t>64686860</t>
         </is>
       </c>
       <c r="B52" t="inlineStr"/>
       <c r="C52" t="inlineStr">
         <is>
-          <t>本田 MSX125 汽油 2座 125cc 自動波 2014 $12,800 1 936</t>
+          <t>本田 FL5 TYPE R 汽油 4座 1996cc 棍波 2023 $488,001 1 156</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>本田 FREED G	汽油	8座	1496cc	自動波	2010	$36,000	1	12 | 起亞 SORENTO DIESEL GT	柴油	5座	2200cc	自動波	2020	$78,001	0	8 | 平治 C200 AMG	混能	5座	1496cc	自動波	2022	$268,006	0	524</t>
+          <t xml:space="preserve">雷諾 MEGANE RS250 MK3 MONACO GP	汽油	5座	2000cc	棍波	2011	$55,001	0	7713 | 越野路華 DEFENDER 90 P300 HSE	汽油	5座	2000cc	自動波	2021	$648,008	0	3231 | 越野路華 RANGE ROVER AUTOBIOGRAPHY LWB	汽油	5座	5000cc	自動波	2019	$898,008	</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>page_12_line_4877</t>
-        </is>
-      </c>
-      <c r="F52" t="n">
-        <v>12</v>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>2026-03-20 14:02:24</t>
+          <t>page_1_line_4961</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>2026-03-30 12:18:24</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>55410567</t>
+          <t>52260037</t>
         </is>
       </c>
       <c r="B53" t="inlineStr"/>
       <c r="C53" t="inlineStr">
         <is>
-          <t>本田 FREED G 汽油 8座 1496cc 自動波 2010 $36,000 1 12</t>
+          <t>保時捷 997 CARRERA S 汽油 5座 3824cc 自動波 2005 $268,000 1 470</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>福士 TIGUAN ALLSPACE 1.5 TSI	汽油	7座	1498cc	自動波	2021	$137,500	0	851 | 起亞 CARNIVAL PREMIUM	汽油	7座	3470cc	自動波	2021	$177,500	0	2516 | 豐田 VELLFIRE 2.5 FACELIFT ALPHARD	汽油	7座	2500cc	自動波	2021	$268,001	1	2495</t>
+          <t>越野路華 RANGE ROVER AUTOBIOGRAPHY LWB	汽油	5座	5000cc	自動波	2019	$898,008	0	139 | 本田 FL5 TYPE R	汽油	4座	1996cc	棍波	2023	$488,001	1	156 | 萬事得 MAZDA 3 HATCHBACK 2.0T	汽油	5座	2000cc	自動波	2015	$43,801	0	1509</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>page_12_line_4865</t>
-        </is>
-      </c>
-      <c r="F53" t="n">
-        <v>12</v>
-      </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>2026-03-20 14:02:24</t>
+          <t>page_1_line_4969</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>2026-03-30 12:18:24</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>56047643</t>
+          <t>60973441</t>
         </is>
       </c>
       <c r="B54" t="inlineStr"/>
       <c r="C54" t="inlineStr">
         <is>
-          <t>豐田 VELLFIRE 2.5 汽油 7座 2500cc 自動波 2016 $158,002 1 9764</t>
+          <t>豐田 VOXY HYBRID SZ 混能 7座 2000cc 自動波 2023 $325,000 0 683</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>燃炓	座位	動力	傳動	年份	售價	留言	瀏覽	已售 | 平治 E200 AMG FACELIFT	汽油	5座	1991cc	自動波	2021	$219,000	2	3957 | 豐田 HIACE 3.0	柴油	6座	3000cc	棍波	2015	$109,900	1	1462</t>
+          <t>本田 FL5 TYPE R	汽油	4座	1996cc	棍波	2023	$488,001	1	156 | 萬事得 MAZDA 3 HATCHBACK 2.0T	汽油	5座	2000cc	自動波	2015	$43,801	0	1509 | 保時捷 997 CARRERA S	汽油	5座	3824cc	自動波	2005	$268,000	1	470</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>page_12_line_4817</t>
-        </is>
-      </c>
-      <c r="F54" t="n">
-        <v>12</v>
-      </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>2026-03-20 14:02:24</t>
+          <t>page_1_line_4973</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>2026-03-30 12:18:24</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>63330917</t>
+          <t>51728941</t>
         </is>
       </c>
       <c r="B55" t="inlineStr"/>
       <c r="C55" t="inlineStr">
         <is>
-          <t>寶馬 520i M SPORT FACELIFT 汽油 5座 1998cc 自動波 2021 $198,000 1 2641</t>
+          <t>寶馬 M3 汽油 4座 3246cc 棍波 2003 $328,000 1 1586</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>豐田 SIENTA G FACELIFT	汽油	7座	1496cc	自動波	2018	$88,200	0	90 | 平治 E250 CAB	汽油	4座	3500cc	自動波	2013	$99,000	1	2119 | 平治 GLC250 4MATIC	汽油	5座	1991cc	自動波	2018	$158,000	0	561</t>
+          <t>本田 STEPWGN HYBRID SPADA	混能	7座	2000cc	自動波	2020	$173,000	0	2441 | 萬事得 MX5 ROADSTER RF	汽油	2座	2000cc	自動波	2018	$165,000	0	4391 | 凌志 IS250C	汽油	4座	2500cc	自動波	2010	$33,800	0	360</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>page_12_line_4837</t>
-        </is>
-      </c>
-      <c r="F55" t="n">
-        <v>12</v>
-      </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>2026-03-20 14:02:24</t>
+          <t>page_1_line_4997</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>2026-03-30 12:18:24</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>63737703</t>
+          <t>68869058</t>
         </is>
       </c>
       <c r="B56" t="inlineStr"/>
       <c r="C56" t="inlineStr">
         <is>
-          <t>平治 C200 AMG 混能 5座 1496cc 自動波 2022 $268,006 0 524</t>
+          <t>平治 SLK350 汽油 2座 3500cc 自動波 2011 $52,000 3 386</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>豐田 VELLFIRE 2.5 FACELIFT ALPHARD	汽油	7座	2500cc	自動波	2021	$268,001	1	2495 | 本田 FREED G	汽油	8座	1496cc	自動波	2010	$36,000	1	12 | 起亞 SORENTO DIESEL GT	柴油	5座	2200cc	自動波	2020	$78,001	0	8</t>
+          <t>燃炓	座位	動力	傳動	年份	售價	留言	瀏覽	已售 | 平治 SLK350	汽油	2座	3500cc	自動波	2011	$52,000	3	386 | 豐田 ALPHARD 2.5 FACELIFT	汽油	7座	2493cc	自動波	2018	$268,000	0	445</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>page_12_line_4873</t>
-        </is>
-      </c>
-      <c r="F56" t="n">
-        <v>12</v>
-      </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>2026-03-20 14:02:24</t>
+          <t>page_1_line_4930</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>2026-03-30 02:11:52</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>91608108</t>
+          <t>92829639</t>
         </is>
       </c>
       <c r="B57" t="inlineStr"/>
       <c r="C57" t="inlineStr">
         <is>
-          <t>豐田 VELLFIRE 2.5 FACELIFT ALPHARD 汽油 7座 2500cc 自動波 2021 $268,001 1 2495</t>
+          <t>豐田 ALPHARD 2.5 FACELIFT 汽油 7座 2493cc 自動波 2018 $268,000 0 445</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>凌志 RX450H HYBRID	混能	7座	3456cc	自動波	2019	$337,500	0	541 | 福士 TIGUAN ALLSPACE 1.5 TSI	汽油	7座	1498cc	自動波	2021	$137,500	0	851 | 起亞 CARNIVAL PREMIUM	汽油	7座	3470cc	自動波	2021	$177,500	0	2516</t>
+          <t>燃炓	座位	動力	傳動	年份	售價	留言	瀏覽	已售 | 平治 SLK350	汽油	2座	3500cc	自動波	2011	$52,000	3	386 | 豐田 ALPHARD 2.5 FACELIFT	汽油	7座	2493cc	自動波	2018	$268,000	0	445</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>page_12_line_4861</t>
-        </is>
-      </c>
-      <c r="F57" t="n">
-        <v>12</v>
-      </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>2026-03-20 14:02:24</t>
+          <t>page_1_line_4934</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>2026-03-30 02:11:52</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>92994046</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr"/>
+          <t>54943269</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>yuyuyu335500@gmail.com</t>
+        </is>
+      </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>起亞 SORENTO DIESEL GT 柴油 5座 2200cc 自動波 2020 $78,001 0 8</t>
+          <t>豐田 VOXY HYBRID SZ 混能 7座 1800cc 自動波 2015 $95,000 0 5</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>起亞 CARNIVAL PREMIUM	汽油	7座	3470cc	自動波	2021	$177,500	0	2516 | 豐田 VELLFIRE 2.5 FACELIFT ALPHARD	汽油	7座	2500cc	自動波	2021	$268,001	1	2495 | 本田 FREED G	汽油	8座	1496cc	自動波	2010	$36,000	1	12</t>
+          <t>寶馬 X5 XDRIVE40iA XLINE	汽油	7座	2998cc	自動波	2020	$298,000	0	442 | 豐田 ALPHARD 3.5 SC FACELIFT	汽油	7座	3500cc	自動波	2020	$348,000	0	1416 | 豐田 VOXY HYBRID ZS FACELIFT NOAH	混能	7座	1800cc	自動波	2017	$128,000	0	2757</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>page_12_line_4869</t>
-        </is>
-      </c>
-      <c r="F58" t="n">
-        <v>12</v>
-      </c>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>2026-03-20 14:02:24</t>
+          <t>page_1_line_4962</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>2026-03-30 02:11:52</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>94818436</t>
+          <t>90103014</t>
         </is>
       </c>
       <c r="B59" t="inlineStr"/>
       <c r="C59" t="inlineStr">
         <is>
-          <t>豐田 SIENTA G FACELIFT 汽油 7座 1496cc 自動波 2018 $88,200 0 90</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>豐田 HIACE 3.0	柴油	6座	3000cc	棍波	2015	$109,900	1	1462 | 豐田 VELLFIRE 2.5	汽油	7座	2500cc	自動波	2016	$158,002	1	9764 | 豐田 PRIUS 1.8 HYBRID	汽油	5座	1800cc	自動波	2016	$79,900	1	5864</t>
-        </is>
-      </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>page_12_line_4825</t>
-        </is>
-      </c>
-      <c r="F59" t="n">
-        <v>12</v>
-      </c>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>2026-03-20 14:02:24</t>
+          <t>本田 STEPWGN 2.0 RK5 SPADA	汽油	7座	2000cc	自動波	2013	$49,001	0	4608</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr"/>
+      <c r="E59" t="inlineStr"/>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>2026-03-20 14:04:42</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>65057591</t>
+          <t>55032890</t>
         </is>
       </c>
       <c r="B60" t="inlineStr"/>
       <c r="C60" t="inlineStr">
         <is>
-          <t>寶馬 430iA COUPE M SPORT 汽油 4座 1998cc 自動波 2016 $118,000 1 107</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>任何 AEON 3D350R	汽油	2座	346cc	自動波	2019	$39,801	1	364 | 寶馬 I4 EDRIVE40 M SPORT	電動	5座	105kW	自動波	2024	$358,000	0	579 | 豐田 VELLFIRE 2.5 FACELIFT ALPHARD	汽油	7座	2500cc	自動波	2019	$228,000	0	5945</t>
-        </is>
-      </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>page_13_line_4869</t>
-        </is>
-      </c>
-      <c r="F60" t="n">
-        <v>13</v>
-      </c>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t>2026-03-20 14:02:34</t>
+          <t>豐田 NOAH HYBRID FACELIFT	混能	7座	1800cc	自動波	2018	$148,000	0	1246</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr"/>
+      <c r="E60" t="inlineStr"/>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>2026-03-20 14:04:42</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>67347555</t>
+          <t>56206667</t>
         </is>
       </c>
       <c r="B61" t="inlineStr"/>
       <c r="C61" t="inlineStr">
         <is>
-          <t>鈴木 GSXS1000GT 汽油 2座 999cc 棍波 2022 $75,000 0 10</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>本田 PCX150	汽油	2座	150cc	自動波	2014	$13,800	1	171 | 豐田 ALPHARD 2.5 HYBRID MODELLISTA	混能	7座	2500cc	自動波	2021	$378,000	0	838 | 日產 SERENA EPOWER Highway Star VIP	混能	7座	1200cc	自動波	2022	$188,000	0	1945</t>
-        </is>
-      </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>page_13_line_4833</t>
-        </is>
-      </c>
-      <c r="F61" t="n">
-        <v>13</v>
-      </c>
-      <c r="G61" t="inlineStr">
-        <is>
-          <t>2026-03-20 14:02:34</t>
+          <t>豐田 NOAH HYBRID FACELIFT	混能	7座	1800cc	自動波	2018	$148,000	0	1246</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr"/>
+      <c r="E61" t="inlineStr"/>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>2026-03-20 14:04:42</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>67414095</t>
+          <t>51809082</t>
         </is>
       </c>
       <c r="B62" t="inlineStr"/>
       <c r="C62" t="inlineStr">
         <is>
-          <t>日產 ELGRAND 2.5 Highway Star 汽油 7座 2500cc 自動波 2015 $68,000 0 6</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>萬事得 CX5 2.5 ISPECIAL	汽油	5座	2488cc	自動波	2019	$98,006	0	337 | 寶馬 X1 SDRIVE18iA XLINE	汽油	5座	1499cc	自動波	2021	$148,006	0	1137 | 豐田 Corolla SPORT HYBRID GZ 213	混能	5座	1800cc	自動波	2026	$148,000	0	8</t>
-        </is>
-      </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>page_13_line_4849</t>
-        </is>
-      </c>
-      <c r="F62" t="n">
-        <v>13</v>
-      </c>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>2026-03-20 14:02:34</t>
+          <t>豐田 NOAH HYBRID FACELIFT	混能	7座	1800cc	自動波	2018	$148,000	0	1246</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr"/>
+      <c r="E62" t="inlineStr"/>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>2026-03-20 14:04:42</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>90334418</t>
+          <t>94666496</t>
         </is>
       </c>
       <c r="B63" t="inlineStr"/>
       <c r="C63" t="inlineStr">
         <is>
-          <t>豐田 VELLFIRE 2.5 FACELIFT ALPHARD 汽油 7座 2500cc 自動波 2019 $228,000 0 5945</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>凌志 RX450H HYBRID	混能	5座	3456cc	自動波	2009	$60,000	0	10 | 任何 AEON 3D350R	汽油	2座	346cc	自動波	2019	$39,801	1	364 | 寶馬 I4 EDRIVE40 M SPORT	電動	5座	105kW	自動波	2024	$358,000	0	579</t>
-        </is>
-      </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>page_13_line_4865</t>
-        </is>
-      </c>
-      <c r="F63" t="n">
-        <v>13</v>
-      </c>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>2026-03-20 14:02:34</t>
+          <t>奧迪 TTS QUATTRO FACELIFT	汽油	4座	2000cc	自動波	2019	$268,000	1	325</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr"/>
+      <c r="E63" t="inlineStr"/>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>2026-03-20 14:04:42</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>91223676</t>
+          <t>62919820</t>
         </is>
       </c>
       <c r="B64" t="inlineStr"/>
       <c r="C64" t="inlineStr">
         <is>
-          <t>寶馬 I4 EDRIVE40 M SPORT 電動 5座 105kW 自動波 2024 $358,000 0 579</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>日產 ELGRAND 2.5 Highway Star	汽油	7座	2500cc	自動波	2015	$68,000	0	6 | 凌志 RX450H HYBRID	混能	5座	3456cc	自動波	2009	$60,000	0	10 | 任何 AEON 3D350R	汽油	2座	346cc	自動波	2019	$39,801	1	364</t>
-        </is>
-      </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>page_13_line_4861</t>
-        </is>
-      </c>
-      <c r="F64" t="n">
-        <v>13</v>
-      </c>
-      <c r="G64" t="inlineStr">
-        <is>
-          <t>2026-03-20 14:02:34</t>
+          <t>保時捷 PANAMERA 4S	汽油	4座	4806cc	自動波	2011	$138,000	0	1467</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr"/>
+      <c r="E64" t="inlineStr"/>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>2026-03-20 14:04:42</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>93789916</t>
+          <t>91212285</t>
         </is>
       </c>
       <c r="B65" t="inlineStr"/>
       <c r="C65" t="inlineStr">
         <is>
-          <t>凌志 RX450H HYBRID 混能 5座 3456cc 自動波 2009 $60,000 0 10</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>寶馬 X1 SDRIVE18iA XLINE	汽油	5座	1499cc	自動波	2021	$148,006	0	1137 | 豐田 Corolla SPORT HYBRID GZ 213	混能	5座	1800cc	自動波	2026	$148,000	0	8 | 日產 ELGRAND 2.5 Highway Star	汽油	7座	2500cc	自動波	2015	$68,000	0	6</t>
-        </is>
-      </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>page_13_line_4853</t>
-        </is>
-      </c>
-      <c r="F65" t="n">
-        <v>13</v>
-      </c>
-      <c r="G65" t="inlineStr">
-        <is>
-          <t>2026-03-20 14:02:34</t>
+          <t>豐田 PRIUS 1.8 HYBRID	混能	5座	1800cc	自動波	2014	$46,900	0	3073</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr"/>
+      <c r="E65" t="inlineStr"/>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>2026-03-20 14:04:42</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>95888746</t>
+          <t>65097433</t>
         </is>
       </c>
       <c r="B66" t="inlineStr"/>
       <c r="C66" t="inlineStr">
         <is>
-          <t>豐田 VOXY HYBRID FACELIFT 混能 7座 1800cc 自動波 2018 $153,009 1 971</t>
-        </is>
-      </c>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>寶馬 I4 EDRIVE40 M SPORT	電動	5座	105kW	自動波	2024	$358,000	0	579 | 豐田 VELLFIRE 2.5 FACELIFT ALPHARD	汽油	7座	2500cc	自動波	2019	$228,000	0	5945 | 寶馬 430iA COUPE M SPORT	汽油	4座	1998cc	自動波	2016	$118,000	1	107</t>
-        </is>
-      </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>page_13_line_4873</t>
-        </is>
-      </c>
-      <c r="F66" t="n">
-        <v>13</v>
-      </c>
-      <c r="G66" t="inlineStr">
-        <is>
-          <t>2026-03-20 14:02:34</t>
+          <t>本田 FIT GE8 RS	汽油	5座	1496cc	棍波	2012	$38,000	3	313</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr"/>
+      <c r="E66" t="inlineStr"/>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>2026-03-20 14:04:42</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>96629822</t>
+          <t>54121990</t>
         </is>
       </c>
       <c r="B67" t="inlineStr"/>
       <c r="C67" t="inlineStr">
         <is>
-          <t>豐田 ALPHARD 2.5 HYBRID MODELLISTA 混能 7座 2500cc 自動波 2021 $378,000 0 838</t>
-        </is>
-      </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>寶馬 X4 XDRIVE30i M SPORT	汽油	5座	1998cc	自動波	2018	$169,000	1	850 | JEEP WRANGLER SAHARA	汽油	5座	3604cc	自動波	2016	$218,006	0	100 | 本田 PCX150	汽油	2座	150cc	自動波	2014	$13,800	1	171</t>
-        </is>
-      </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>page_13_line_4825</t>
-        </is>
-      </c>
-      <c r="F67" t="n">
-        <v>13</v>
-      </c>
-      <c r="G67" t="inlineStr">
-        <is>
-          <t>2026-03-20 14:02:34</t>
+          <t>凌志 UX200 ULTIMATE	汽油	5座	1987cc	自動波	2019	$108,000	1	9</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr"/>
+      <c r="E67" t="inlineStr"/>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>2026-03-20 14:04:31</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>97557197</t>
+          <t>95426595</t>
         </is>
       </c>
       <c r="B68" t="inlineStr"/>
       <c r="C68" t="inlineStr">
         <is>
-          <t>寶馬 X4 XDRIVE30i M SPORT 汽油 5座 1998cc 自動波 2018 $169,000 1 850</t>
-        </is>
-      </c>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>燃炓	座位	動力	傳動	年份	售價	留言	瀏覽	已售 | 任何 Z125PRO	汽油	2座	125cc	棍波	2016	$16,801	2	121 | 寶馬 X4 XDRIVE30i M SPORT	汽油	5座	1998cc	自動波	2018	$169,000	1	850</t>
-        </is>
-      </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>page_13_line_4813</t>
-        </is>
-      </c>
-      <c r="F68" t="n">
-        <v>13</v>
-      </c>
-      <c r="G68" t="inlineStr">
-        <is>
-          <t>2026-03-20 14:02:34</t>
+          <t>特斯拉 MODEL 3 LONG RANGE LR	電動	5座	153kW	自動波	2024	$188,000	1	21</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr"/>
+      <c r="E68" t="inlineStr"/>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>2026-03-20 14:04:31</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>68466877</t>
+          <t>63889738</t>
         </is>
       </c>
       <c r="B69" t="inlineStr"/>
       <c r="C69" t="inlineStr">
         <is>
-          <t>豐田 ALPHARD 2.5 SC 汽油 7座 2500cc 自動波 2018 $258,000 0 7</t>
-        </is>
-      </c>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t>豐田 ALPHARD 2.5 FACELIFT VELLFIRE	汽油	7座	2500cc	自動波	2016	$188,000	0	4151 | 寶馬 X3 XDRIVE20iA XLINE	汽油	5座	1998cc	自動波	2019	$148,000	0	51 | 豐田 VELLFIRE 2.5 HYBRID EXL	汽油	7座	2500cc	自動波	2024	$788,000	0	983</t>
-        </is>
-      </c>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>page_14_line_4825</t>
-        </is>
-      </c>
-      <c r="F69" t="n">
-        <v>14</v>
-      </c>
-      <c r="G69" t="inlineStr">
-        <is>
-          <t>2026-03-20 14:02:44</t>
+          <t>豐田 VOXY HYBRID MODELLISTA	混能	7座	1800cc	自動波	2019	$197,999	1	46</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr"/>
+      <c r="E69" t="inlineStr"/>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>2026-03-20 14:04:31</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>69994006</t>
+          <t>60211006</t>
         </is>
       </c>
       <c r="B70" t="inlineStr"/>
       <c r="C70" t="inlineStr">
         <is>
-          <t>豐田 VELLFIRE 2.5 HYBRID EXL 汽油 7座 2500cc 自動波 2024 $788,000 0 983</t>
-        </is>
-      </c>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>燃炓	座位	動力	傳動	年份	售價	留言	瀏覽	已售 | 寶馬 X1 SDRIVE18iA M SPORT	汽油	5座	1499cc	自動波	2019	$108,000	0	119 | 豐田 ALPHARD 2.5 FACELIFT VELLFIRE	汽油	7座	2500cc	自動波	2016	$188,000	0	4151</t>
-        </is>
-      </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>page_14_line_4821</t>
-        </is>
-      </c>
-      <c r="F70" t="n">
-        <v>14</v>
-      </c>
-      <c r="G70" t="inlineStr">
-        <is>
-          <t>2026-03-20 14:02:44</t>
+          <t>豐田 GR YARIS RC	汽油	4座	1600cc	棍波	2021	$448,000	0	310</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr"/>
+      <c r="E70" t="inlineStr"/>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>2026-03-20 14:04:31</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>98058787</t>
+          <t>60562494</t>
         </is>
       </c>
       <c r="B71" t="inlineStr"/>
       <c r="C71" t="inlineStr">
         <is>
-          <t>寶馬 X1 SDRIVE18iA M SPORT 汽油 5座 1500cc 自動波 2019 $88,000 0 4</t>
-        </is>
-      </c>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>豐田 PRIUS 1.8 HYBRID S	混能	5座	1800cc	自動波	2018	$103,009	1	3350 | 豐田 VELLFIRE 2.5 HYBRID	混能	7座	2500cc	自動波	2024	$678,000	0	408 | 日產 SERENA EPOWER	混能	7座	1433cc	自動波	2024	$308,001	1	2267</t>
-        </is>
-      </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>page_14_line_4841</t>
-        </is>
-      </c>
-      <c r="F71" t="n">
-        <v>14</v>
-      </c>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t>2026-03-20 14:02:44</t>
+          <t>賓利 CONTINENTAL GT GTC	汽油	4座	5950cc	自動波	2020	$1,880,001	1	2303</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr"/>
+      <c r="E71" t="inlineStr"/>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>2026-03-20 14:04:31</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>93102644</t>
+          <t>96620811</t>
         </is>
       </c>
       <c r="B72" t="inlineStr"/>
       <c r="C72" t="inlineStr">
         <is>
-          <t>寶馬 318iA SALOON SPORT	汽油	5座	1998cc	自動波	2021	$138,000	1	985</t>
+          <t>豐田 ALPHARD 2.5 HYBRID MODELLISTA	混能	7座	2500cc	自動波	2022	$408,000	0	165</t>
         </is>
       </c>
       <c r="D72" t="inlineStr"/>
       <c r="E72" t="inlineStr"/>
-      <c r="F72" t="n">
-        <v>15</v>
-      </c>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t>2026-03-20 14:03:48</t>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>2026-03-20 14:04:31</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>60230929</t>
+          <t>52959192</t>
         </is>
       </c>
       <c r="B73" t="inlineStr"/>
       <c r="C73" t="inlineStr">
         <is>
-          <t>本田 FORZA 300	汽油	2座	279cc	自動波	2019	$30,000	1	11</t>
+          <t>本田 FREED GB3	汽油	5座	1500cc	自動波	2013	$43,000	0	8</t>
         </is>
       </c>
       <c r="D73" t="inlineStr"/>
       <c r="E73" t="inlineStr"/>
-      <c r="F73" t="n">
-        <v>16</v>
-      </c>
-      <c r="G73" t="inlineStr">
-        <is>
-          <t>2026-03-20 14:03:59</t>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>2026-03-20 14:04:31</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>91577771</t>
+          <t>66110239</t>
         </is>
       </c>
       <c r="B74" t="inlineStr"/>
       <c r="C74" t="inlineStr">
         <is>
-          <t>凌志 IS300H	混能	5座	2499cc	自動波	2013	$78,000	0	5</t>
+          <t>日產 ENV200	電動	7座	80kW	自動波	2019	$99,000	0	2943</t>
         </is>
       </c>
       <c r="D74" t="inlineStr"/>
       <c r="E74" t="inlineStr"/>
-      <c r="F74" t="n">
-        <v>16</v>
-      </c>
-      <c r="G74" t="inlineStr">
-        <is>
-          <t>2026-03-20 14:03:59</t>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>2026-03-20 14:04:31</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>98822456</t>
+          <t>66445335</t>
         </is>
       </c>
       <c r="B75" t="inlineStr"/>
       <c r="C75" t="inlineStr">
         <is>
-          <t>豐田 bB	汽油	5座	1496cc	自動波	2005	$33,000	0	13</t>
+          <t>奧迪 A4 AVANT SLINE	汽油	5座	1800cc	自動波	2004	$34,000	4	1142</t>
         </is>
       </c>
       <c r="D75" t="inlineStr"/>
       <c r="E75" t="inlineStr"/>
-      <c r="F75" t="n">
-        <v>16</v>
-      </c>
-      <c r="G75" t="inlineStr">
-        <is>
-          <t>2026-03-20 14:03:59</t>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>2026-03-20 14:04:31</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>61691818</t>
+          <t>69163096</t>
         </is>
       </c>
       <c r="B76" t="inlineStr"/>
       <c r="C76" t="inlineStr">
         <is>
-          <t>保時捷 CAYENNE	汽油	5座	3000cc	自動波	2018	$418,000	1	7</t>
+          <t>平治 C250	汽油	5座	1800cc	自動波	2012	$28,500	1	644</t>
         </is>
       </c>
       <c r="D76" t="inlineStr"/>
       <c r="E76" t="inlineStr"/>
-      <c r="F76" t="n">
-        <v>17</v>
-      </c>
-      <c r="G76" t="inlineStr">
-        <is>
-          <t>2026-03-20 14:04:10</t>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>2026-03-20 14:04:21</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>95101257</t>
+          <t>66018900</t>
         </is>
       </c>
       <c r="B77" t="inlineStr"/>
       <c r="C77" t="inlineStr">
         <is>
-          <t>平治 E200 COUPE	汽油	4座	1991cc	自動波	2014	$58,001	1	1523</t>
+          <t>寶馬 C650 GT	汽油	2座	647cc	自動波	2013	$32,888	2	1306</t>
         </is>
       </c>
       <c r="D77" t="inlineStr"/>
       <c r="E77" t="inlineStr"/>
-      <c r="F77" t="n">
-        <v>17</v>
-      </c>
-      <c r="G77" t="inlineStr">
-        <is>
-          <t>2026-03-20 14:04:10</t>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>2026-03-20 14:04:21</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>98899907</t>
+          <t>65766550</t>
         </is>
       </c>
       <c r="B78" t="inlineStr"/>
       <c r="C78" t="inlineStr">
         <is>
-          <t>豐田 VELLFIRE 3.5 ZG FACELIFT	汽油	7座	3456cc	自動波	2019	$318,000	1	374</t>
+          <t>平治 E200 AVANTGARDE FACELIFT	汽油	5座	2000cc	自動波	2013	$48,800	0	11</t>
         </is>
       </c>
       <c r="D78" t="inlineStr"/>
       <c r="E78" t="inlineStr"/>
-      <c r="F78" t="n">
-        <v>17</v>
-      </c>
-      <c r="G78" t="inlineStr">
-        <is>
-          <t>2026-03-20 14:04:10</t>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>2026-03-20 14:04:21</t>
         </is>
       </c>
     </row>
@@ -2942,10 +2546,7 @@
       </c>
       <c r="D79" t="inlineStr"/>
       <c r="E79" t="inlineStr"/>
-      <c r="F79" t="n">
-        <v>18</v>
-      </c>
-      <c r="G79" t="inlineStr">
+      <c r="F79" t="inlineStr">
         <is>
           <t>2026-03-20 14:04:21</t>
         </is>
@@ -2954,21 +2555,18 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>65766550</t>
+          <t>90308495</t>
         </is>
       </c>
       <c r="B80" t="inlineStr"/>
       <c r="C80" t="inlineStr">
         <is>
-          <t>平治 E200 AVANTGARDE FACELIFT	汽油	5座	2000cc	自動波	2013	$48,800	0	11</t>
+          <t>豐田 SPADE	汽油	5座	1500cc	自動波	2018	$56,000	0	13</t>
         </is>
       </c>
       <c r="D80" t="inlineStr"/>
       <c r="E80" t="inlineStr"/>
-      <c r="F80" t="n">
-        <v>18</v>
-      </c>
-      <c r="G80" t="inlineStr">
+      <c r="F80" t="inlineStr">
         <is>
           <t>2026-03-20 14:04:21</t>
         </is>
@@ -2977,21 +2575,18 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>66018900</t>
+          <t>97897433</t>
         </is>
       </c>
       <c r="B81" t="inlineStr"/>
       <c r="C81" t="inlineStr">
         <is>
-          <t>寶馬 C650 GT	汽油	2座	647cc	自動波	2013	$32,888	2	1306</t>
+          <t>豐田 Celica	汽油	5座	2000cc	自動波	1990	$1,000	8	4398</t>
         </is>
       </c>
       <c r="D81" t="inlineStr"/>
       <c r="E81" t="inlineStr"/>
-      <c r="F81" t="n">
-        <v>18</v>
-      </c>
-      <c r="G81" t="inlineStr">
+      <c r="F81" t="inlineStr">
         <is>
           <t>2026-03-20 14:04:21</t>
         </is>
@@ -3000,460 +2595,2232 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>69163096</t>
+          <t>61691818</t>
         </is>
       </c>
       <c r="B82" t="inlineStr"/>
       <c r="C82" t="inlineStr">
         <is>
-          <t>平治 C250	汽油	5座	1800cc	自動波	2012	$28,500	1	644</t>
+          <t>保時捷 CAYENNE	汽油	5座	3000cc	自動波	2018	$418,000	1	7</t>
         </is>
       </c>
       <c r="D82" t="inlineStr"/>
       <c r="E82" t="inlineStr"/>
-      <c r="F82" t="n">
-        <v>18</v>
-      </c>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t>2026-03-20 14:04:21</t>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>2026-03-20 14:04:10</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>90308495</t>
+          <t>95101257</t>
         </is>
       </c>
       <c r="B83" t="inlineStr"/>
       <c r="C83" t="inlineStr">
         <is>
-          <t>豐田 SPADE	汽油	5座	1500cc	自動波	2018	$56,000	0	13</t>
+          <t>平治 E200 COUPE	汽油	4座	1991cc	自動波	2014	$58,001	1	1523</t>
         </is>
       </c>
       <c r="D83" t="inlineStr"/>
       <c r="E83" t="inlineStr"/>
-      <c r="F83" t="n">
-        <v>18</v>
-      </c>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t>2026-03-20 14:04:21</t>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>2026-03-20 14:04:10</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>97897433</t>
+          <t>98899907</t>
         </is>
       </c>
       <c r="B84" t="inlineStr"/>
       <c r="C84" t="inlineStr">
         <is>
-          <t>豐田 Celica	汽油	5座	2000cc	自動波	1990	$1,000	8	4398</t>
+          <t>豐田 VELLFIRE 3.5 ZG FACELIFT	汽油	7座	3456cc	自動波	2019	$318,000	1	374</t>
         </is>
       </c>
       <c r="D84" t="inlineStr"/>
       <c r="E84" t="inlineStr"/>
-      <c r="F84" t="n">
-        <v>18</v>
-      </c>
-      <c r="G84" t="inlineStr">
-        <is>
-          <t>2026-03-20 14:04:21</t>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>2026-03-20 14:04:10</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>52959192</t>
+          <t>91577771</t>
         </is>
       </c>
       <c r="B85" t="inlineStr"/>
       <c r="C85" t="inlineStr">
         <is>
-          <t>本田 FREED GB3	汽油	5座	1500cc	自動波	2013	$43,000	0	8</t>
+          <t>凌志 IS300H	混能	5座	2499cc	自動波	2013	$78,000	0	5</t>
         </is>
       </c>
       <c r="D85" t="inlineStr"/>
       <c r="E85" t="inlineStr"/>
-      <c r="F85" t="n">
-        <v>19</v>
-      </c>
-      <c r="G85" t="inlineStr">
-        <is>
-          <t>2026-03-20 14:04:31</t>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>2026-03-20 14:03:59</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>54121990</t>
+          <t>98822456</t>
         </is>
       </c>
       <c r="B86" t="inlineStr"/>
       <c r="C86" t="inlineStr">
         <is>
-          <t>凌志 UX200 ULTIMATE	汽油	5座	1987cc	自動波	2019	$108,000	1	9</t>
+          <t>豐田 bB	汽油	5座	1496cc	自動波	2005	$33,000	0	13</t>
         </is>
       </c>
       <c r="D86" t="inlineStr"/>
       <c r="E86" t="inlineStr"/>
-      <c r="F86" t="n">
-        <v>19</v>
-      </c>
-      <c r="G86" t="inlineStr">
-        <is>
-          <t>2026-03-20 14:04:31</t>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>2026-03-20 14:03:59</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>60211006</t>
+          <t>60230929</t>
         </is>
       </c>
       <c r="B87" t="inlineStr"/>
       <c r="C87" t="inlineStr">
         <is>
-          <t>豐田 GR YARIS RC	汽油	4座	1600cc	棍波	2021	$448,000	0	310</t>
+          <t>本田 FORZA 300	汽油	2座	279cc	自動波	2019	$30,000	1	11</t>
         </is>
       </c>
       <c r="D87" t="inlineStr"/>
       <c r="E87" t="inlineStr"/>
-      <c r="F87" t="n">
-        <v>19</v>
-      </c>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t>2026-03-20 14:04:31</t>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>2026-03-20 14:03:59</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>60562494</t>
+          <t>93102644</t>
         </is>
       </c>
       <c r="B88" t="inlineStr"/>
       <c r="C88" t="inlineStr">
         <is>
-          <t>賓利 CONTINENTAL GT GTC	汽油	4座	5950cc	自動波	2020	$1,880,001	1	2303</t>
+          <t>寶馬 318iA SALOON SPORT	汽油	5座	1998cc	自動波	2021	$138,000	1	985</t>
         </is>
       </c>
       <c r="D88" t="inlineStr"/>
       <c r="E88" t="inlineStr"/>
-      <c r="F88" t="n">
-        <v>19</v>
-      </c>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t>2026-03-20 14:04:31</t>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>2026-03-20 14:03:48</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>63889738</t>
+          <t>69994006</t>
         </is>
       </c>
       <c r="B89" t="inlineStr"/>
       <c r="C89" t="inlineStr">
         <is>
-          <t>豐田 VOXY HYBRID MODELLISTA	混能	7座	1800cc	自動波	2019	$197,999	1	46</t>
-        </is>
-      </c>
-      <c r="D89" t="inlineStr"/>
-      <c r="E89" t="inlineStr"/>
-      <c r="F89" t="n">
-        <v>19</v>
-      </c>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>2026-03-20 14:04:31</t>
+          <t>豐田 VELLFIRE 2.5 HYBRID EXL 汽油 7座 2500cc 自動波 2024 $788,000 0 983</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>燃炓	座位	動力	傳動	年份	售價	留言	瀏覽	已售 | 寶馬 X1 SDRIVE18iA M SPORT	汽油	5座	1499cc	自動波	2019	$108,000	0	119 | 豐田 ALPHARD 2.5 FACELIFT VELLFIRE	汽油	7座	2500cc	自動波	2016	$188,000	0	4151</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>page_14_line_4821</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>2026-03-20 14:02:44</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>66110239</t>
+          <t>68466877</t>
         </is>
       </c>
       <c r="B90" t="inlineStr"/>
       <c r="C90" t="inlineStr">
         <is>
-          <t>日產 ENV200	電動	7座	80kW	自動波	2019	$99,000	0	2943</t>
-        </is>
-      </c>
-      <c r="D90" t="inlineStr"/>
-      <c r="E90" t="inlineStr"/>
-      <c r="F90" t="n">
-        <v>19</v>
-      </c>
-      <c r="G90" t="inlineStr">
-        <is>
-          <t>2026-03-20 14:04:31</t>
+          <t>豐田 ALPHARD 2.5 SC 汽油 7座 2500cc 自動波 2018 $258,000 0 7</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>豐田 ALPHARD 2.5 FACELIFT VELLFIRE	汽油	7座	2500cc	自動波	2016	$188,000	0	4151 | 寶馬 X3 XDRIVE20iA XLINE	汽油	5座	1998cc	自動波	2019	$148,000	0	51 | 豐田 VELLFIRE 2.5 HYBRID EXL	汽油	7座	2500cc	自動波	2024	$788,000	0	983</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>page_14_line_4825</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>2026-03-20 14:02:44</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>66445335</t>
+          <t>98058787</t>
         </is>
       </c>
       <c r="B91" t="inlineStr"/>
       <c r="C91" t="inlineStr">
         <is>
-          <t>奧迪 A4 AVANT SLINE	汽油	5座	1800cc	自動波	2004	$34,000	4	1142</t>
-        </is>
-      </c>
-      <c r="D91" t="inlineStr"/>
-      <c r="E91" t="inlineStr"/>
-      <c r="F91" t="n">
-        <v>19</v>
-      </c>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t>2026-03-20 14:04:31</t>
+          <t>寶馬 X1 SDRIVE18iA M SPORT 汽油 5座 1500cc 自動波 2019 $88,000 0 4</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>豐田 PRIUS 1.8 HYBRID S	混能	5座	1800cc	自動波	2018	$103,009	1	3350 | 豐田 VELLFIRE 2.5 HYBRID	混能	7座	2500cc	自動波	2024	$678,000	0	408 | 日產 SERENA EPOWER	混能	7座	1433cc	自動波	2024	$308,001	1	2267</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>page_14_line_4841</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>2026-03-20 14:02:44</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>95426595</t>
+          <t>97557197</t>
         </is>
       </c>
       <c r="B92" t="inlineStr"/>
       <c r="C92" t="inlineStr">
         <is>
-          <t>特斯拉 MODEL 3 LONG RANGE LR	電動	5座	153kW	自動波	2024	$188,000	1	21</t>
-        </is>
-      </c>
-      <c r="D92" t="inlineStr"/>
-      <c r="E92" t="inlineStr"/>
-      <c r="F92" t="n">
-        <v>19</v>
-      </c>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t>2026-03-20 14:04:31</t>
+          <t>寶馬 X4 XDRIVE30i M SPORT 汽油 5座 1998cc 自動波 2018 $169,000 1 850</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>燃炓	座位	動力	傳動	年份	售價	留言	瀏覽	已售 | 任何 Z125PRO	汽油	2座	125cc	棍波	2016	$16,801	2	121 | 寶馬 X4 XDRIVE30i M SPORT	汽油	5座	1998cc	自動波	2018	$169,000	1	850</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>page_13_line_4813</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>2026-03-20 14:02:34</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>96620811</t>
+          <t>96629822</t>
         </is>
       </c>
       <c r="B93" t="inlineStr"/>
       <c r="C93" t="inlineStr">
         <is>
-          <t>豐田 ALPHARD 2.5 HYBRID MODELLISTA	混能	7座	2500cc	自動波	2022	$408,000	0	165</t>
-        </is>
-      </c>
-      <c r="D93" t="inlineStr"/>
-      <c r="E93" t="inlineStr"/>
-      <c r="F93" t="n">
-        <v>19</v>
-      </c>
-      <c r="G93" t="inlineStr">
-        <is>
-          <t>2026-03-20 14:04:31</t>
+          <t>豐田 ALPHARD 2.5 HYBRID MODELLISTA 混能 7座 2500cc 自動波 2021 $378,000 0 838</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>寶馬 X4 XDRIVE30i M SPORT	汽油	5座	1998cc	自動波	2018	$169,000	1	850 | JEEP WRANGLER SAHARA	汽油	5座	3604cc	自動波	2016	$218,006	0	100 | 本田 PCX150	汽油	2座	150cc	自動波	2014	$13,800	1	171</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>page_13_line_4825</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>2026-03-20 14:02:34</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>51809082</t>
+          <t>67347555</t>
         </is>
       </c>
       <c r="B94" t="inlineStr"/>
       <c r="C94" t="inlineStr">
         <is>
-          <t>豐田 NOAH HYBRID FACELIFT	混能	7座	1800cc	自動波	2018	$148,000	0	1246</t>
-        </is>
-      </c>
-      <c r="D94" t="inlineStr"/>
-      <c r="E94" t="inlineStr"/>
-      <c r="F94" t="n">
-        <v>20</v>
-      </c>
-      <c r="G94" t="inlineStr">
-        <is>
-          <t>2026-03-20 14:04:42</t>
+          <t>鈴木 GSXS1000GT 汽油 2座 999cc 棍波 2022 $75,000 0 10</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>本田 PCX150	汽油	2座	150cc	自動波	2014	$13,800	1	171 | 豐田 ALPHARD 2.5 HYBRID MODELLISTA	混能	7座	2500cc	自動波	2021	$378,000	0	838 | 日產 SERENA EPOWER Highway Star VIP	混能	7座	1200cc	自動波	2022	$188,000	0	1945</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>page_13_line_4833</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>2026-03-20 14:02:34</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>55032890</t>
+          <t>67414095</t>
         </is>
       </c>
       <c r="B95" t="inlineStr"/>
       <c r="C95" t="inlineStr">
         <is>
-          <t>豐田 NOAH HYBRID FACELIFT	混能	7座	1800cc	自動波	2018	$148,000	0	1246</t>
-        </is>
-      </c>
-      <c r="D95" t="inlineStr"/>
-      <c r="E95" t="inlineStr"/>
-      <c r="F95" t="n">
-        <v>20</v>
-      </c>
-      <c r="G95" t="inlineStr">
-        <is>
-          <t>2026-03-20 14:04:42</t>
+          <t>日產 ELGRAND 2.5 Highway Star 汽油 7座 2500cc 自動波 2015 $68,000 0 6</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>萬事得 CX5 2.5 ISPECIAL	汽油	5座	2488cc	自動波	2019	$98,006	0	337 | 寶馬 X1 SDRIVE18iA XLINE	汽油	5座	1499cc	自動波	2021	$148,006	0	1137 | 豐田 Corolla SPORT HYBRID GZ 213	混能	5座	1800cc	自動波	2026	$148,000	0	8</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>page_13_line_4849</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>2026-03-20 14:02:34</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>56206667</t>
+          <t>93789916</t>
         </is>
       </c>
       <c r="B96" t="inlineStr"/>
       <c r="C96" t="inlineStr">
         <is>
-          <t>豐田 NOAH HYBRID FACELIFT	混能	7座	1800cc	自動波	2018	$148,000	0	1246</t>
-        </is>
-      </c>
-      <c r="D96" t="inlineStr"/>
-      <c r="E96" t="inlineStr"/>
-      <c r="F96" t="n">
-        <v>20</v>
-      </c>
-      <c r="G96" t="inlineStr">
-        <is>
-          <t>2026-03-20 14:04:42</t>
+          <t>凌志 RX450H HYBRID 混能 5座 3456cc 自動波 2009 $60,000 0 10</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>寶馬 X1 SDRIVE18iA XLINE	汽油	5座	1499cc	自動波	2021	$148,006	0	1137 | 豐田 Corolla SPORT HYBRID GZ 213	混能	5座	1800cc	自動波	2026	$148,000	0	8 | 日產 ELGRAND 2.5 Highway Star	汽油	7座	2500cc	自動波	2015	$68,000	0	6</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>page_13_line_4853</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>2026-03-20 14:02:34</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>62919820</t>
+          <t>91223676</t>
         </is>
       </c>
       <c r="B97" t="inlineStr"/>
       <c r="C97" t="inlineStr">
         <is>
-          <t>保時捷 PANAMERA 4S	汽油	4座	4806cc	自動波	2011	$138,000	0	1467</t>
-        </is>
-      </c>
-      <c r="D97" t="inlineStr"/>
-      <c r="E97" t="inlineStr"/>
-      <c r="F97" t="n">
-        <v>20</v>
-      </c>
-      <c r="G97" t="inlineStr">
-        <is>
-          <t>2026-03-20 14:04:42</t>
+          <t>寶馬 I4 EDRIVE40 M SPORT 電動 5座 105kW 自動波 2024 $358,000 0 579</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>日產 ELGRAND 2.5 Highway Star	汽油	7座	2500cc	自動波	2015	$68,000	0	6 | 凌志 RX450H HYBRID	混能	5座	3456cc	自動波	2009	$60,000	0	10 | 任何 AEON 3D350R	汽油	2座	346cc	自動波	2019	$39,801	1	364</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>page_13_line_4861</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>2026-03-20 14:02:34</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>65097433</t>
+          <t>90334418</t>
         </is>
       </c>
       <c r="B98" t="inlineStr"/>
       <c r="C98" t="inlineStr">
         <is>
-          <t>本田 FIT GE8 RS	汽油	5座	1496cc	棍波	2012	$38,000	3	313</t>
-        </is>
-      </c>
-      <c r="D98" t="inlineStr"/>
-      <c r="E98" t="inlineStr"/>
-      <c r="F98" t="n">
-        <v>20</v>
-      </c>
-      <c r="G98" t="inlineStr">
-        <is>
-          <t>2026-03-20 14:04:42</t>
+          <t>豐田 VELLFIRE 2.5 FACELIFT ALPHARD 汽油 7座 2500cc 自動波 2019 $228,000 0 5945</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>凌志 RX450H HYBRID	混能	5座	3456cc	自動波	2009	$60,000	0	10 | 任何 AEON 3D350R	汽油	2座	346cc	自動波	2019	$39,801	1	364 | 寶馬 I4 EDRIVE40 M SPORT	電動	5座	105kW	自動波	2024	$358,000	0	579</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>page_13_line_4865</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>2026-03-20 14:02:34</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>90103014</t>
+          <t>65057591</t>
         </is>
       </c>
       <c r="B99" t="inlineStr"/>
       <c r="C99" t="inlineStr">
         <is>
-          <t>本田 STEPWGN 2.0 RK5 SPADA	汽油	7座	2000cc	自動波	2013	$49,001	0	4608</t>
-        </is>
-      </c>
-      <c r="D99" t="inlineStr"/>
-      <c r="E99" t="inlineStr"/>
-      <c r="F99" t="n">
-        <v>20</v>
-      </c>
-      <c r="G99" t="inlineStr">
-        <is>
-          <t>2026-03-20 14:04:42</t>
+          <t>寶馬 430iA COUPE M SPORT 汽油 4座 1998cc 自動波 2016 $118,000 1 107</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>任何 AEON 3D350R	汽油	2座	346cc	自動波	2019	$39,801	1	364 | 寶馬 I4 EDRIVE40 M SPORT	電動	5座	105kW	自動波	2024	$358,000	0	579 | 豐田 VELLFIRE 2.5 FACELIFT ALPHARD	汽油	7座	2500cc	自動波	2019	$228,000	0	5945</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>page_13_line_4869</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>2026-03-20 14:02:34</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>91212285</t>
+          <t>95888746</t>
         </is>
       </c>
       <c r="B100" t="inlineStr"/>
       <c r="C100" t="inlineStr">
         <is>
-          <t>豐田 PRIUS 1.8 HYBRID	混能	5座	1800cc	自動波	2014	$46,900	0	3073</t>
-        </is>
-      </c>
-      <c r="D100" t="inlineStr"/>
-      <c r="E100" t="inlineStr"/>
-      <c r="F100" t="n">
-        <v>20</v>
-      </c>
-      <c r="G100" t="inlineStr">
-        <is>
-          <t>2026-03-20 14:04:42</t>
+          <t>豐田 VOXY HYBRID FACELIFT 混能 7座 1800cc 自動波 2018 $153,009 1 971</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>寶馬 I4 EDRIVE40 M SPORT	電動	5座	105kW	自動波	2024	$358,000	0	579 | 豐田 VELLFIRE 2.5 FACELIFT ALPHARD	汽油	7座	2500cc	自動波	2019	$228,000	0	5945 | 寶馬 430iA COUPE M SPORT	汽油	4座	1998cc	自動波	2016	$118,000	1	107</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>page_13_line_4873</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>2026-03-20 14:02:34</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>94666496</t>
+          <t>56047643</t>
         </is>
       </c>
       <c r="B101" t="inlineStr"/>
       <c r="C101" t="inlineStr">
         <is>
-          <t>奧迪 TTS QUATTRO FACELIFT	汽油	4座	2000cc	自動波	2019	$268,000	1	325</t>
-        </is>
-      </c>
-      <c r="D101" t="inlineStr"/>
-      <c r="E101" t="inlineStr"/>
-      <c r="F101" t="n">
-        <v>20</v>
-      </c>
-      <c r="G101" t="inlineStr">
-        <is>
-          <t>2026-03-20 14:04:42</t>
+          <t>豐田 VELLFIRE 2.5 汽油 7座 2500cc 自動波 2016 $158,002 1 9764</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>燃炓	座位	動力	傳動	年份	售價	留言	瀏覽	已售 | 平治 E200 AMG FACELIFT	汽油	5座	1991cc	自動波	2021	$219,000	2	3957 | 豐田 HIACE 3.0	柴油	6座	3000cc	棍波	2015	$109,900	1	1462</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>page_12_line_4817</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>2026-03-20 14:02:24</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>94818436</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr"/>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>豐田 SIENTA G FACELIFT 汽油 7座 1496cc 自動波 2018 $88,200 0 90</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>豐田 HIACE 3.0	柴油	6座	3000cc	棍波	2015	$109,900	1	1462 | 豐田 VELLFIRE 2.5	汽油	7座	2500cc	自動波	2016	$158,002	1	9764 | 豐田 PRIUS 1.8 HYBRID	汽油	5座	1800cc	自動波	2016	$79,900	1	5864</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>page_12_line_4825</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>2026-03-20 14:02:24</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>63330917</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr"/>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>寶馬 520i M SPORT FACELIFT 汽油 5座 1998cc 自動波 2021 $198,000 1 2641</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>豐田 SIENTA G FACELIFT	汽油	7座	1496cc	自動波	2018	$88,200	0	90 | 平治 E250 CAB	汽油	4座	3500cc	自動波	2013	$99,000	1	2119 | 平治 GLC250 4MATIC	汽油	5座	1991cc	自動波	2018	$158,000	0	561</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>page_12_line_4837</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>2026-03-20 14:02:24</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>91608108</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr"/>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>豐田 VELLFIRE 2.5 FACELIFT ALPHARD 汽油 7座 2500cc 自動波 2021 $268,001 1 2495</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>凌志 RX450H HYBRID	混能	7座	3456cc	自動波	2019	$337,500	0	541 | 福士 TIGUAN ALLSPACE 1.5 TSI	汽油	7座	1498cc	自動波	2021	$137,500	0	851 | 起亞 CARNIVAL PREMIUM	汽油	7座	3470cc	自動波	2021	$177,500	0	2516</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>page_12_line_4861</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>2026-03-20 14:02:24</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>55410567</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr"/>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>本田 FREED G 汽油 8座 1496cc 自動波 2010 $36,000 1 12</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>福士 TIGUAN ALLSPACE 1.5 TSI	汽油	7座	1498cc	自動波	2021	$137,500	0	851 | 起亞 CARNIVAL PREMIUM	汽油	7座	3470cc	自動波	2021	$177,500	0	2516 | 豐田 VELLFIRE 2.5 FACELIFT ALPHARD	汽油	7座	2500cc	自動波	2021	$268,001	1	2495</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>page_12_line_4865</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>2026-03-20 14:02:24</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>92994046</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr"/>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>起亞 SORENTO DIESEL GT 柴油 5座 2200cc 自動波 2020 $78,001 0 8</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>起亞 CARNIVAL PREMIUM	汽油	7座	3470cc	自動波	2021	$177,500	0	2516 | 豐田 VELLFIRE 2.5 FACELIFT ALPHARD	汽油	7座	2500cc	自動波	2021	$268,001	1	2495 | 本田 FREED G	汽油	8座	1496cc	自動波	2010	$36,000	1	12</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>page_12_line_4869</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>2026-03-20 14:02:24</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>63737703</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr"/>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>平治 C200 AMG 混能 5座 1496cc 自動波 2022 $268,006 0 524</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>豐田 VELLFIRE 2.5 FACELIFT ALPHARD	汽油	7座	2500cc	自動波	2021	$268,001	1	2495 | 本田 FREED G	汽油	8座	1496cc	自動波	2010	$36,000	1	12 | 起亞 SORENTO DIESEL GT	柴油	5座	2200cc	自動波	2020	$78,001	0	8</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>page_12_line_4873</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>2026-03-20 14:02:24</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>27082922</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr"/>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>本田 MSX125 汽油 2座 125cc 自動波 2014 $12,800 1 936</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>本田 FREED G	汽油	8座	1496cc	自動波	2010	$36,000	1	12 | 起亞 SORENTO DIESEL GT	柴油	5座	2200cc	自動波	2020	$78,001	0	8 | 平治 C200 AMG	混能	5座	1496cc	自動波	2022	$268,006	0	524</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>page_12_line_4877</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>2026-03-20 14:02:24</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>56266366</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr"/>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>豐田 ALPHARD 2.5Z 汽油 7座 2493cc 自動波 2023 $528,008 0 734</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>燃炓	座位	動力	傳動	年份	售價	留言	瀏覽	已售 | 奧迪 Q7 40 TFSI QUATTRO	汽油	7座	2000cc	自動波	2019	$148,000	1	187 | 迷你 MINI Cooper COUNTRYMAN	汽油	5座	1598cc	自動波	2016	$58,001	1	98</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>page_11_line_4817</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>2026-03-20 14:02:14</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>61112699</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr"/>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>保時捷 911 CARRERA 2S 991.2 汽油 4座 3000cc 自動波 2016 $997,999 0 137</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>豐田 ALPHARD 2.5Z	汽油	7座	2493cc	自動波	2023	$528,008	0	734 | 豐田 ALPHARD 3.5 GF	汽油	7座	3500cc	自動波	2015	$178,000	1	43 | 豐田 ALPHARD 3.5 EXECUTIVE LOUNGE	汽油	7座	3500cc	自動波	2020	$378,001	1	164</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>page_11_line_4829</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>2026-03-20 14:02:14</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>98889889</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr"/>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>起亞 SORENTO DIESEL 柴油 7座 2200cc 自動波 2017 $119,000 1 6622</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>豐田 ALPHARD 3.5 GF	汽油	7座	3500cc	自動波	2015	$178,000	1	43 | 豐田 ALPHARD 3.5 EXECUTIVE LOUNGE	汽油	7座	3500cc	自動波	2020	$378,001	1	164 | 保時捷 911 CARRERA 2S 991.2	汽油	4座	3000cc	自動波	2016	$997,999	0	137</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>page_11_line_4833</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>2026-03-20 14:02:14</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>91312375</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr"/>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>本田 NSX NC1 汽油 2座 3493cc 自動波 2016 $2,279,999 1 2785</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>保時捷 911 CARRERA 2S 991.2	汽油	4座	3000cc	自動波	2016	$997,999	0	137 | 起亞 SORENTO DIESEL	柴油	7座	2200cc	自動波	2017	$119,000	1	6622 | 本田 NSX NC1	汽油	2座	3493cc	自動波	2016	$2,279,999	1	2785</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>page_11_line_4841</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>2026-03-20 14:02:14</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>98660834</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr"/>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>特斯拉 MODEL 3 SR PLUS 電動 5座 88kW 自動波 2019 $89,000 0 147</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>豐田 PRIUS 1.8 HYBRID	混能	5座	1800cc	自動波	2013	$33,800	1	2309 | 本田 FD2 TYPE R	汽油	4座	1998cc	棍波	2009	$159,000	1	6149 | 法拉利 CALIFORNIA T	汽油	5座	3800cc	自動波	2015	$947,999	0	241</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>page_11_line_4877</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>2026-03-20 14:02:14</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>61123032</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr"/>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>豐田 VOXY HYBRID ZS FACELIFT NOAH 混能 7座 1800cc 自動波 2016 $90,001 1 4085</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>本田 FD2 TYPE R	汽油	4座	1998cc	棍波	2009	$159,000	1	6149 | 法拉利 CALIFORNIA T	汽油	5座	3800cc	自動波	2015	$947,999	0	241 | 特斯拉 MODEL 3 SR PLUS	電動	5座	88kW	自動波	2019	$89,000	0	147</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>page_11_line_4881</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>2026-03-20 14:02:14</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>98549548</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr"/>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>起亞 SORENTO DIESEL 柴油 5座 2200cc 自動波 2019 $64,000 3 368</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>豐田 ALPHARD 2.5 Z	汽油	7座	2500cc	自動波	2026	$698,001	1	357 | 豐田 ALPHARD 3.5 GF	汽油	7座	3500cc	自動波	2018	$298,000	1	1006 | 豐田 ALPHARD 2.5 Z	汽油	7座	2500cc	自動波	2025	$668,000	1	740</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>page_10_line_4837</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>2026-03-20 14:02:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>98886669</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr"/>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>豐田 ALPHARD 2.5Z 汽油 7座 2493cc 自動波 2026 $668,000 0 319</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>平治 GLA200 AMG FACELIFT	汽油	5座	2000cc	自動波	2019	$95,801	1	155 | 任何 GAC HYPTEC HT ULTRA PLUS	電動	5座	83kW	自動波	2026	$299,000	1	288 | 本田 CRV 1.5 Turbo	汽油	7座	1500cc	自動波	2025	$285,000	1	1080</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>page_10_line_4865</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>2026-03-20 14:02:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>61997777</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr"/>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>寶馬 430iA COUPE M SPORT EDITION 汽油 4座 2000cc 自動波 2019 $156,001 1 266</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>平治 S400 HYBRID	汽油	5座	3498cc	自動波	2014	$158,000	0	719 | 豐田 VELLFIRE 2.4 Turbo Z PREMIER	汽油	7座	2400cc	自動波	2026	$858,000	1	204 | 寶馬 430iA COUPE M SPORT EDITION	汽油	4座	2000cc	自動波	2019	$156,001	1	266</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>page_10_line_4881</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>2026-03-20 14:02:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>53937499</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>bubu666999111@gmail.com</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>豐田 HIACE 300 柴油 5座 2755cc 自動波 2022 $265,000 0 2</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>燃炓	座位	動力	傳動	年份	售價	留言	瀏覽	已售 | 本田 STEPWGN HYBRID RP5	混能	7座	2000cc	自動波	2022	$188,000	1	2160 | 豐田 HIACE 300	柴油	5座	2755cc	自動波	2022	$265,000	0	2</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>page_9_line_4813</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>2026-03-20 14:01:54</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>91498709</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>bubu666999111@gmail.com</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>寶馬 220iA ACTIVE TOURER 汽油 5座 1998cc 自動波 2015 $40,008 0 1995</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>豐田 HIACE 300	柴油	5座	2755cc	自動波	2022	$265,000	0	2 | 日產 FAIRLADY Z33 350Z	汽油	2座	3498cc	棍波	2003	$45,000	0	2415 | 車爽、good handling、保養佳、內外新淨、手數高、... (由於已售，聯絡人資料亦被保護中。)</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>page_9_line_4825</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>2026-03-20 14:01:54</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>66699911</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>bubu666999111@gmail.com</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>豐田 VOXY HYBRID NOAH 汽油 7座 1800cc 自動波 2015 $88,001 1 2091</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>日產 FAIRLADY Z33 350Z	汽油	2座	3498cc	棍波	2003	$45,000	0	2415 | 車爽、good handling、保養佳、內外新淨、手數高、... (由於已售，聯絡人資料亦被保護中。) | 起亞 SORENTO	汽油	7座	2400cc	自動波	2015	$55,000	1	245</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>page_9_line_4829</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>2026-03-20 14:01:54</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>93793325</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>bubu666999111@gmail.com</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>豐田 VOXY HYBRID ZS FACELIFT NOAH 混能 7座 1800cc 自動波 2015 $88,001 0 8252</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>豐田 VOXY HYBRID NOAH	汽油	7座	1800cc	自動波	2015	$88,001	1	2091 | 未出牌🚗 keyless 頂級版 皮座 正廠...，Lam 電郵:bubu666999111@gmail.com | 凌志 CT200H F SPORT	混能	5座	1798cc	自動波	2012	$45,008	1	2881</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>page_9_line_4841</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>2026-03-20 14:01:54</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>61276373</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>bubu666999111@gmail.com</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>寶馬 X3 20i FACELIFT 汽油 5座 1998cc 自動波 2022 $259,000 1 922</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>寶馬 X3 XDRIVE20iA XLINE	汽油	5座	1998cc	自動波	2018	$98,000	0	1273 | 豐田 VELLFIRE 2.5 FACELIFT	汽油	7座	2500cc	自動波	2016	$158,000	0	3215 | 豐田 VELLFIRE 2.5 FACELIFT	汽油	7座	2500cc	自動波	2018	$178,001	0	2462</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>page_9_line_4857</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>2026-03-20 14:01:54</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>53074323</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr"/>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>豐田 VOXY HYBRID ZS FACELIFT 混能 7座 1800cc 自動波 2019 $178,000 0 4</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>豐田 VELLFIRE 3.5 ZG FACELIFT	汽油	7座	3500cc	自動波	2020	$318,001	1	3345 | 富士 FORESTER 2.0XT	汽油	5座	2000cc	自動波	2015	$48,008	0	1289 | 豐田 VELLFIRE 2.5 FACELIFT ALPHARD	汽油	7座	2500cc	自動波	2019	$248,001	0	3497</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>page_9_line_4873</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>2026-03-20 14:01:54</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>53601171</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr"/>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>奧迪 A5 40TFSI SLINE AVANT 汽油 5座 2000cc 自動波 2025 $458,001 1 893</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>豐田 VELLFIRE 2.5 FACELIFT ALPHARD	汽油	7座	2500cc	自動波	2019	$248,001	0	3497 | 豐田 VOXY HYBRID ZS FACELIFT	混能	7座	1800cc	自動波	2019	$178,000	0	4 | 日野 500	柴油	3座	7684cc	棍波	2013	$240,000	0	54</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>page_9_line_4881</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>2026-03-20 14:01:54</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>60722845</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr"/>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>豐田 ALPHARD 3.5 汽油 7座 3456cc 自動波 2009 $48,000 0 78</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>豐田 VOXY HYBRID ZS FACELIFT	混能	7座	1800cc	自動波	2019	$178,000	0	4 | 日野 500	柴油	3座	7684cc	棍波	2013	$240,000	0	54 | 車斗3米8、27尺長、13年 16ton 無死期 (由於已售，聯絡人資料亦被保護中。)</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>page_9_line_4885</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>2026-03-20 14:01:54</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>97902449</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>yusonyuson79@gmail.com</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>豐田 Previa DELUXE 汽油 8座 2400cc 自動波 2014 $59,000 1 766</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>豐田 VELLFIRE 2.5 FACELIFT ALPHARD	汽油	7座	2500cc	自動波	2020	$258,001	1	6856 | 同場多架現貨、未出牌、四電動記憶中櫈、三電動門...，Yuson 電郵:yusonyuson79@gmail.com | 豐田 VOXY HYBRID NOAH	混能	7座	1800cc	自動波	2018	$117,801	1	2934</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>page_8_line_4869</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>2026-03-20 14:01:44</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>68211289</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr"/>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>豐田 ALPHARD EXECUTIVE LOUNGE 汽油 7座 3456cc 自動波 2020 $368,800 0 384</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>燃炓	座位	動力	傳動	年份	售價	留言	瀏覽	已售 | 寶馬 318iA SALOON SPORT	汽油	5座	2000cc	自動波	2021	$132,000	1	2886 | 豐田 NOAH 1.8 HYBRID	混能	7座	1800cc	自動波	2018	$163,000	1	821</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>page_7_line_4817</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>2026-03-20 14:01:35</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>59663109</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr"/>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>快意 ABARTH 595C 汽油 4座 1368cc 自動波 2013 $75,000 0 4</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>燃炓	座位	動力	傳動	年份	售價	留言	瀏覽	已售 | 寶馬 318iA SALOON SPORT	汽油	5座	2000cc	自動波	2021	$132,000	1	2886 | 豐田 NOAH 1.8 HYBRID	混能	7座	1800cc	自動波	2018	$163,000	1	821</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>page_7_line_4821</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>2026-03-20 14:01:35</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>66382688</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>yoyo168@myyahoo.com</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>迷你 MINI Cooper 汽油 5座 1490cc 自動波 2019 $86,000 1 405</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>豐田 ALPHARD 2.5 HYBRID HEV	混能	7座	2500cc	自動波	2023	$688,008	1	948 | 豐田 VELLFIRE 2.5 HYBRID	混能	7座	2493cc	自動波	2024	$678,800	0	394 | 豐田 VELLFIRE EXECUTIVE LOUNGE	汽油	7座	2493cc	自動波	2024	$788,800	0	315</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>page_7_line_4841</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>2026-03-20 14:01:35</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>90880900</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>ying89614@gmail.com</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>保時捷 CAYMAN S 汽油 2座 3400cc 自動波 2006 $79,000 0 371</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>豐田 VELLFIRE 2.5 ZG	汽油	7座	2500cc	自動波	2017	$228,008	1	697 | 豐田 VELLFIRE 3.5 ZG JBL	汽油	7座	3500cc	自動波	2019	$348,000	1	405 | 黑色 雙天窗 3電門 4電坐 冷暖坐 空氣淨化 JBL音響 ...，JS 電郵:js17@myyahoo.com</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>page_6_line_4845</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>2026-03-20 14:01:24</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>63453124</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>ying89614@gmail.com</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>豐田 VELLFIRE 2.5 汽油 8座 2500cc 自動波 2015 $138,001 0 1672</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>平治 GLC250 4MATIC AMG	汽油	5座	2000cc	自動波	2018	$118,001	0	44 | 保時捷 CAYMAN S	汽油	2座	3400cc	自動波	2006	$79,000	0	371 | 本田 FREED HYBRID GB7	混能	6座	1500cc	自動波	2020	$122,000	1	2893</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>page_6_line_4853</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>2026-03-20 14:01:24</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>94616278</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>js17@myyahoo.com</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>豐田 Previa AERAS 汽油 7座 2362cc 自動波 2014 $49,000 0 1095</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>豐田 VELLFIRE 2.5	汽油	8座	2500cc	自動波	2015	$138,001	0	1672 | 豐田 PRIUS 1.8 HYBRID	混能	5座	1800cc	自動波	2019	$128,888	1	3203 | 白色黑頂 Keyless 恆溫冷氣 DVD BT音響 泊車鏡...，JS 電郵:js17@myyahoo.com</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>page_6_line_4865</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>2026-03-20 14:01:24</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>59655535</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>georgeli9099@gmail.com</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>豐田 ALPHARD 3.5 汽油 7座 3456cc 自動波 2017 $238,000 0 161</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>燃炓	座位	動力	傳動	年份	售價	留言	瀏覽	已售 | 豐田 SPADE 1.5	汽油	5座	1500cc	自動波	2012	$38,000	1	60 | 行貨1字 7萬9公里 趟門上落方便 空間闊落 360泊車 內...，HO LUN YING 電郵:georgeli9099@gmail.com</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>page_5_line_4817</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>2026-03-20 14:01:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>98751864</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>georgeli9099@gmail.com</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>本田 SHUTTLE HYBRID GP7 混能 5座 1496cc 自動波 2015 $60,000 1 522</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>豐田 ALPHARD 3.5	汽油	7座	3456cc	自動波	2017	$238,000	0	161 | 豐田 ALPHARD 2.5 Z	汽油	7座	2500cc	自動波	2025	$578,000	1	701 | 豐田 HIACE	柴油	6座	2755cc	自動波	2022	$238,000	0	218</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>page_5_line_4829</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>2026-03-20 14:01:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>53218551</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>js66@myyahoo.com</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>萬事得 CX9 汽油 7座 2500cc 自動波 2019 $108,000 0 16</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>本田 FREED HYBRID	混能	7座	1496cc	自動波	2017	$87,888	1	1162 | 豐田 VELLFIRE 3.5 WELCAB	汽油	7座	3500cc	自動波	2016	$188,000	1	770 | 豐田 ESQUIRE HYBRID GI	混能	7座	1800cc	自動波	2019	$198,888	1	2465</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>page_5_line_4853</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>2026-03-20 14:01:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>92220890</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>js66@myyahoo.com</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>豐田 GR86 RC 汽油 4座 2400cc 棍波 2025 $318,000 1 9320</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>豐田 VELLFIRE 2.5 ALPHARD	汽油	8座	2498cc	自動波	2015	$147,888	1	539 | 豐田 GR86 RC	汽油	4座	2400cc	棍波	2025	$318,000	1	9320 | 25制 白色 全新車 現貨 改良款 Eyesight系統 泊...，RR CHAN 電郵:js66@myyahoo.com</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>page_5_line_4873</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>2026-03-20 14:01:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>94856084</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>js321@myyahoo.com</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>凌志 UX200 ULTIMATE 混能 5座 2000cc 自動波 2020 $108,000 0 2</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>豐田 YARIS HYBRID Z MODELLISTA	混能	5座	1500cc	自動波	2021	$148,000	1	2491 | Z版 黑籠 雙暖座 CarPlay音響 360鏡頭 前後感應...，YY Chung 電郵:js321@myyahoo.com | 豐田 VELLFIRE3.5	汽油	7座	3500cc	自動波	2014	$90,000	3	237</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>page_4_line_4837</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>2026-03-20 14:01:05</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>62589888</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>js321@myyahoo.com</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>豐田 ALPHARD 2.5 汽油 7座 2500cc 自動波 2023 $518,000 0 3</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>豐田 VELLFIRE3.5	汽油	7座	3500cc	自動波	2014	$90,000	3	237 | 2014、汽油7座、5萬多公里、原版原漆、车况... (由於已售，聯絡人資料亦被保護中。) | 保時捷 MACAN 2.0	汽油	5座	2000cc	自動波	2015	$109,999	1	67</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>page_4_line_4841</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>2026-03-20 14:01:05</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>67262528</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>georgeli9099@gmail.com</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>富豪 XC90 T6 INSCRIPTION 汽油 7座 1969cc 自動波 2017 $168,000 0 2</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t xml:space="preserve">豐田 VELLFIRE 2.5 ALPHARD	汽油	7座	2500cc	自動波	2021	$267,990	1	155 | 20落地 1字 6萬km 中凳大班椅 雙天窗 中排吊螢幕 3...，HO LUN YING 電郵:georgeli9099@gmail.com | 豐田 SIENTA HYBRID G MODELLISTA	混能	7座	1500cc	自動波	2018	$118,000	1	</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>page_4_line_4857</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>2026-03-20 14:01:05</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>65838610</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>georgeli9099@gmail.com</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>豐田 LAND CRUISER 250 Prado VX 汽油 7座 2700cc 自動波 2025 $699,009 1 11138</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>豐田 PREIVA AERAS	汽油	7座	2400cc	自動波	2013	$57,999	1	10 | 行貨13製 牌費到七月中 實用家庭七座位 重心低 3電門 雙...，HO LUN YING 電郵:georgeli9099@gmail.com | 富豪 XC90 T6 INSCRIPTION	汽油	7座	1969cc	自動波	2017	$168,000	0	2</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>page_4_line_4865</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>2026-03-20 14:01:05</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>46229124</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>georgeli9099@gmail.com</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>豐田 ALPHARD 3.5 汽油 7座 3456cc 自動波 2016 $238,000 0 17</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>富豪 XC90 T6 INSCRIPTION	汽油	7座	1969cc	自動波	2017	$168,000	0	2 | 豐田 LAND CRUISER 250 Prado VX	汽油	7座	2700cc	自動波	2025	$699,009	1	11138 | 25制 全新車 現貨 天窗 黑皮籠 冷暖電坐 前後恆溫 36...，Go 電郵:gogo28@myyahoo.com</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>page_4_line_4869</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>2026-03-20 14:01:05</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>91664985</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>js321@myyahoo.com</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr"/>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>燃炓	座位	動力	傳動	年份	售價	留言	瀏覽	已售 | 任何 YAMAHA TMAX500	汽油	2座	499cc	自動波	2006	$18,800	1	2782 | 本田 CB190R	汽油	2座	184cc	棍波	2016	$15,800	1	2042</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>page_3_line_4809</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>2026-03-20 14:00:55</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>62190476</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>js321@myyahoo.com</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>寶馬 218iA GRAN TOURER 汽油 7座 1499cc 自動波 2018 $50,000 0 47</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>任何 KAWASAKI ZX10R	汽油	2座	998cc	棍波	2006	$32,800	1	265 | 特斯拉 85D	電動	5座	158kW	自動波	2015	$108,000	0	2 | 豐田 VOXY HYBRID FACELIFT NOAH	混能	7座	1800cc	自動波	2021	$208,000	1	1605</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>page_3_line_4833</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>2026-03-20 14:00:55</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>54346258</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>js321@myyahoo.com</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>平治 S580L AMG 汽油 5座 4000cc 自動波 2023 $1,680,000 0 1236</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>豐田 VOXY HYBRID FACELIFT NOAH	混能	7座	1800cc	自動波	2021	$208,000	1	1605 | 尾期 黑蓬頂 雙電門 雙暖座 USB插頭 DVDBT音響 泊...，YY Chung 電郵:js321@myyahoo.com | 寶馬 218iA GRAN TOURER	汽油	7座	1499cc	自動波	2018	$50,000	0	47</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>page_3_line_4841</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>2026-03-20 14:00:55</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>66172222</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>js321@myyahoo.com</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>豐田 ALPHARD 3.5 汽油 7座 3500cc 自動波 2019 $279,000 0 1721</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>凌志 NX300H	混能	5座	2494cc	自動波	2015	$82,000	1	607 | 豐田 ALPHARD 2.5 HYBRID SRC JBL	混能	7座	2500cc	自動波	2019	$368,888	1	1159 | 雙天窗 3電門 4電坐 前後冷暖坐 閱讀燈 JBL音響 後排...，YY Chung 電郵:js321@myyahoo.com</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>page_3_line_4869</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>2026-03-20 14:00:55</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>90925106</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>js321@myyahoo.com</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>奧迪 A3 SPORTBACK 35 TFSI SLINE 汽油 5座 1498cc 自動波 2021 $128,000 3 134</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>豐田 ALPHARD 2.5 HYBRID SRC JBL	混能	7座	2500cc	自動波	2019	$368,888	1	1159 | 雙天窗 3電門 4電坐 前後冷暖坐 閱讀燈 JBL音響 後排...，YY Chung 電郵:js321@myyahoo.com | 五十鈴 PICK UP	柴油	5座	2499cc	自動波	2015	$93,000	2	1037</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>page_3_line_4873</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>2026-03-20 14:00:55</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>62559898</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr"/>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>本田 FREED HYBRID 混能 6座 1500cc 自動波 2012 $45,000 0 1395</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>保時捷 GT3 RS	汽油	2座	3600cc	棍波	2007	$1,475,000	1	4966 | 豐田 ALPHARD 3.5 SC FACELIFT	汽油	7座	3500cc	自動波	2022	$389,000	1	1707 | 本田 FREED HYBRID	混能	6座	1500cc	自動波	2012	$45,000	0	1395</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>page_2_line_4881</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>2026-03-20 14:00:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>95006400</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr"/>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>五十鈴 MVD 柴油 3座 5200cc 棍波 2016 $180,000 0 0</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>燃炓	座位	動力	傳動	年份	售價	留言	瀏覽	已售 | 五十鈴 MVD	柴油	3座	5200cc	棍波	2016	$180,000	0	0 | 五十鈴 24TONNES	柴油	3座	15681cc	棍波	2019	$427,800	0	346</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>page_1_line_4809</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>2026-03-20 14:00:35</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>91232229</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>car88@myyahoo.com</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>迷你 MINI Cooper S ROADSTER 汽油 2座 1598cc 自動波 2014 $148,000 0 169</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>燃炓	座位	動力	傳動	年份	售價	留言	瀏覽	已售 | 五十鈴 MVD	柴油	3座	5200cc	棍波	2016	$180,000	0	0 | 五十鈴 24TONNES	柴油	3座	15681cc	棍波	2019	$427,800	0	346</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>page_1_line_4821</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>2026-03-20 14:00:35</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>90787669</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>car88@myyahoo.com</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>五十鈴 5.5TONNES 柴油 3座 5193cc 棍波 2017 $188,000 0 1156</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>燃炓	座位	動力	傳動	年份	售價	留言	瀏覽	已售 | 五十鈴 5.5TONNES	柴油	3座	5193cc	棍波	2017	$188,000	0	1156 | 五十鈴 5.5TONNES	柴油	3座	5193cc	棍波	2015	$148,000	0	1045</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>page_1_line_4809</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>2026-03-20 13:58:38</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>60878617</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>car88@myyahoo.com</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>凌志 GS200T 2.0 Turbo 汽油 5座 2000cc 自動波 2017 $105,800 0 42</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>五十鈴 5.5TONNES	柴油	3座	5193cc	棍波	2015	$148,000	0	1045 | 鈴木 Jimny JB74W	汽油	4座	1500cc	自動波	2024	$178,888	1	123 | 行貨 自動波 恆溫冷氣 Alpine音響 360鏡頭 mor...，Vins 電郵:car88@myyahoo.com</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>page_1_line_4821</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>2026-03-20 13:58:38</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>98835057</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>car88@myyahoo.com</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>豐田 PRIUS 1.8 HYBRID S 混能 5座 1800cc 自動波 2018 $128,000 0 888</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>任何 R3	汽油	2座	300cc	棍波	2016	$15,000	1	1244 | 有意WhatsApp、牌費到7月、要換消耗品 (由於已售，聯絡人資料亦被保護中。) | 大發 WAKE G NBOX	汽油	4座	660cc	自動波	2018	$68,888	1	91</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>page_1_line_4833</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>2026-03-20 13:58:38</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>59766617</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>car88@myyahoo.com</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>平治 190 E2.5 16V 汽油 4座 2498cc 自動波 1989 $268,000 1 97</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>大發 WAKE G NBOX	汽油	4座	660cc	自動波	2018	$68,888	1	91 | 彩籃色 雙電門 3缸Turbo 恆溫冷氣 Android音響...，Vins 電郵:car88@myyahoo.com | 豐田 PRIUS 1.8 HYBRID S	混能	5座	1800cc	自動波	2018	$128,000	0	888</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>page_1_line_4837</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>2026-03-20 13:58:38</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>98088522</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>car88@myyahoo.com</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>平治 E250 CAB E200 汽油 4座 2000cc 自動波 2015 $78,800 1 2609</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>平治 190 E2.5 16V	汽油	4座	2498cc	自動波	1989	$268,000	1	97 | 豐田 VOXY HYBRID ZS NOAH	混能	7座	1800cc	自動波	2019	$188,008	2	964 | 白色 黑皮 雙電門 電尾冚 Alpine音響 ...，Vins 電郵:car88@myyahoo.com</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>page_1_line_4845</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>2026-03-20 13:58:38</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>90703526</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>car88@myyahoo.com</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>五十鈴 5.5TONNES 柴油 3座 5193cc 棍波 2022 $326,800 1 280</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>豐田 VOXY HYBRID ZS NOAH	混能	7座	1800cc	自動波	2019	$188,008	2	964 | 白色 黑皮 雙電門 電尾冚 Alpine音響 ...，Vins 電郵:car88@myyahoo.com | 平治 E250 CAB E200	汽油	4座	2000cc	自動波	2015	$78,800	1	2609</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>page_1_line_4849</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>2026-03-20 13:58:38</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>61822201</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>car88@myyahoo.com</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>豐田 ALPHARD ZA 汽油 7座 2500cc 自動波 2020 $248,000 1 3902</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>本田 ODYSSEY HYBRID ABSOLUTE EX	混能	7座	2000cc	自動波	2018	$138,000	1	3187 | 豐田 ALPHARD 2.5 SC VELLFIRE	汽油	7座	2500cc	自動波	2023	$388,008	1	1108 | 黑色 雙天窗 3電門 4電坐 冷暖坐 空氣淨化 DVD BT...，Vins 電郵:car88@myyahoo.com</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>page_1_line_4861</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>2026-03-20 13:58:38</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>91750024</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>car88@myyahoo.com</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>豐田 NOAH 90 汽油 7座 1987cc 自動波 2023 $269,000 0 4562</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>豐田 ALPHARD 2.5 SC VELLFIRE	汽油	7座	2500cc	自動波	2023	$388,008	1	1108 | 黑色 雙天窗 3電門 4電坐 冷暖坐 空氣淨化 DVD BT...，Vins 電郵:car88@myyahoo.com | 豐田 ALPHARD ZA	汽油	7座	2500cc	自動波	2020	$248,000	1	3902</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>page_1_line_4865</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>2026-03-20 13:58:38</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>62633422</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>car88@myyahoo.com</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>保時捷 BOXSTER S 汽油 2座 3400cc 自動波 2006 $75,000 0 3741</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>豐田 GR86 RZ EYESIGHT	汽油	4座	2400cc	棍波	2024	$398,000	0	401 | 豐田 VELLFIRE ZG	汽油	7座	2500cc	自動波	2016	$178,000	1	2124 | 保時捷 BOXSTER S	汽油	2座	3400cc	自動波	2006	$75,000	0	3741</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>page_1_line_4885</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>2026-03-20 13:58:38</t>
         </is>
       </c>
     </row>
